--- a/dataset/a5-rawdata.xlsx
+++ b/dataset/a5-rawdata.xlsx
@@ -7134,7 +7134,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -7183,6 +7183,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -7664,31 +7671,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7697,119 +7701,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7834,6 +7841,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7889,10 +7897,7 @@
   <dxfs count="1">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
+        <patternFill patternType="none"/>
       </fill>
     </dxf>
   </dxfs>
@@ -8210,7 +8215,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="2" ht="18.75" customHeight="1" spans="1:10">
       <c r="A2" s="4">
         <v>522</v>
       </c>
@@ -8232,7 +8237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="3" ht="18.75" customHeight="1" spans="1:10">
       <c r="A3" s="4">
         <v>421</v>
       </c>
@@ -8254,7 +8259,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="4" ht="18.75" customHeight="1" spans="1:10">
       <c r="A4" s="4">
         <v>359</v>
       </c>
@@ -8276,7 +8281,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:10">
+    <row r="5" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A5" s="1">
         <v>205</v>
       </c>
@@ -8300,7 +8305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:10">
+    <row r="6" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A6" s="4">
         <v>612</v>
       </c>
@@ -8324,7 +8329,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:10">
+    <row r="7" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A7" s="4">
         <v>611</v>
       </c>
@@ -8348,7 +8353,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:10">
+    <row r="8" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A8" s="4">
         <v>372</v>
       </c>
@@ -8372,7 +8377,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:10">
+    <row r="9" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -8398,7 +8403,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:10">
+    <row r="10" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A10" s="1">
         <v>317</v>
       </c>
@@ -8422,7 +8427,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:10">
+    <row r="11" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A11" s="4">
         <v>405</v>
       </c>
@@ -8446,7 +8451,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:10">
+    <row r="12" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A12" s="1">
         <v>268</v>
       </c>
@@ -8470,7 +8475,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:10">
+    <row r="13" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A13" s="4">
         <v>373</v>
       </c>
@@ -8494,7 +8499,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:10">
+    <row r="14" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A14" s="1">
         <v>193</v>
       </c>
@@ -8518,7 +8523,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:10">
+    <row r="15" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A15" s="1">
         <v>273</v>
       </c>
@@ -8542,7 +8547,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:10">
+    <row r="16" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A16" s="4">
         <v>358</v>
       </c>
@@ -8566,7 +8571,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:10">
+    <row r="17" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A17" s="1">
         <v>275</v>
       </c>
@@ -8590,7 +8595,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:10">
+    <row r="18" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A18" s="4">
         <v>370</v>
       </c>
@@ -8614,7 +8619,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:10">
+    <row r="19" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A19" s="1">
         <v>192</v>
       </c>
@@ -8638,7 +8643,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:10">
+    <row r="20" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A20" s="1">
         <v>42</v>
       </c>
@@ -8662,7 +8667,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:10">
+    <row r="21" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -8688,7 +8693,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:10">
+    <row r="22" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A22" s="4">
         <v>417</v>
       </c>
@@ -8712,7 +8717,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:10">
+    <row r="23" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A23" s="1">
         <v>329</v>
       </c>
@@ -8736,7 +8741,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:10">
+    <row r="24" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A24" s="1">
         <v>216</v>
       </c>
@@ -8760,7 +8765,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:10">
+    <row r="25" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A25" s="4">
         <v>422</v>
       </c>
@@ -8784,7 +8789,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:10">
+    <row r="26" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A26" s="1">
         <v>188</v>
       </c>
@@ -8807,7 +8812,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:10">
+    <row r="27" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A27" s="1">
         <v>183</v>
       </c>
@@ -8830,7 +8835,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:10">
+    <row r="28" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A28" s="4">
         <v>366</v>
       </c>
@@ -8853,7 +8858,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:10">
+    <row r="29" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A29" s="4">
         <v>369</v>
       </c>
@@ -8876,7 +8881,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:10">
+    <row r="30" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A30" s="1">
         <v>174</v>
       </c>
@@ -8899,7 +8904,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:10">
+    <row r="31" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A31" s="1">
         <v>187</v>
       </c>
@@ -8922,7 +8927,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:10">
+    <row r="32" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A32" s="1">
         <v>175</v>
       </c>
@@ -8945,7 +8950,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:10">
+    <row r="33" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A33" s="1">
         <v>176</v>
       </c>
@@ -8968,7 +8973,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:10">
+    <row r="34" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="1">
         <v>35</v>
       </c>
@@ -8991,7 +8996,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:10">
+    <row r="35" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -9017,7 +9022,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:10">
+    <row r="36" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="4">
         <v>591</v>
       </c>
@@ -9040,7 +9045,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="37" ht="18.75" customHeight="1" spans="1:10">
+    <row r="37" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="4">
         <v>507</v>
       </c>
@@ -9063,7 +9068,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" ht="18.75" customHeight="1" spans="1:10">
+    <row r="38" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="4">
         <v>565</v>
       </c>
@@ -9086,7 +9091,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="39" ht="18.75" customHeight="1" spans="1:10">
+    <row r="39" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="1">
         <v>43</v>
       </c>
@@ -9109,7 +9114,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" ht="18.75" customHeight="1" spans="1:10">
+    <row r="40" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="1">
         <v>44</v>
       </c>
@@ -9132,7 +9137,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="41" ht="18.75" customHeight="1" spans="1:10">
+    <row r="41" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="4">
         <v>643</v>
       </c>
@@ -9155,7 +9160,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="42" ht="18.75" customHeight="1" spans="1:10">
+    <row r="42" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="4">
         <v>414</v>
       </c>
@@ -9178,7 +9183,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" ht="18.75" customHeight="1" spans="1:10">
+    <row r="43" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="4">
         <v>524</v>
       </c>
@@ -9201,7 +9206,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="44" ht="18.75" customHeight="1" spans="1:10">
+    <row r="44" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="1">
         <v>15</v>
       </c>
@@ -9227,7 +9232,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="45" ht="18.75" customHeight="1" spans="1:10">
+    <row r="45" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="4">
         <v>424</v>
       </c>
@@ -9250,7 +9255,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" ht="18.75" customHeight="1" spans="1:10">
+    <row r="46" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="4">
         <v>423</v>
       </c>
@@ -9273,7 +9278,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" ht="18.75" customHeight="1" spans="1:10">
+    <row r="47" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="4">
         <v>499</v>
       </c>
@@ -9296,7 +9301,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" ht="18.75" customHeight="1" spans="1:10">
+    <row r="48" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="4">
         <v>529</v>
       </c>
@@ -9319,7 +9324,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" ht="18.75" customHeight="1" spans="1:10">
+    <row r="49" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A49" s="1">
         <v>61</v>
       </c>
@@ -9342,7 +9347,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" ht="18.75" customHeight="1" spans="1:10">
+    <row r="50" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A50" s="4">
         <v>511</v>
       </c>
@@ -9365,7 +9370,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="51" ht="18.75" customHeight="1" spans="1:10">
+    <row r="51" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A51" s="4">
         <v>570</v>
       </c>
@@ -9388,7 +9393,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" ht="18.75" customHeight="1" spans="1:10">
+    <row r="52" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A52" s="4">
         <v>547</v>
       </c>
@@ -9411,7 +9416,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="53" ht="18.75" customHeight="1" spans="1:10">
+    <row r="53" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A53" s="4">
         <v>580</v>
       </c>
@@ -9434,7 +9439,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="54" ht="18.75" customHeight="1" spans="1:10">
+    <row r="54" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A54" s="1">
         <v>29</v>
       </c>
@@ -9457,7 +9462,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" ht="18.75" customHeight="1" spans="1:10">
+    <row r="55" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A55" s="4">
         <v>610</v>
       </c>
@@ -9480,7 +9485,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="56" ht="18.75" customHeight="1" spans="1:10">
+    <row r="56" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A56" s="1">
         <v>259</v>
       </c>
@@ -9503,7 +9508,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="57" ht="18.75" customHeight="1" spans="1:10">
+    <row r="57" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A57" s="1">
         <v>189</v>
       </c>
@@ -9526,7 +9531,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="58" ht="18.75" customHeight="1" spans="1:10">
+    <row r="58" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A58" s="4">
         <v>409</v>
       </c>
@@ -9549,7 +9554,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="59" ht="18.75" customHeight="1" spans="1:10">
+    <row r="59" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A59" s="4">
         <v>645</v>
       </c>
@@ -9572,7 +9577,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="60" ht="18.75" customHeight="1" spans="1:10">
+    <row r="60" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A60" s="4">
         <v>419</v>
       </c>
@@ -9595,7 +9600,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="61" ht="18.75" customHeight="1" spans="1:10">
+    <row r="61" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A61" s="4">
         <v>583</v>
       </c>
@@ -9618,7 +9623,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="62" ht="18.75" customHeight="1" spans="1:10">
+    <row r="62" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A62" s="1">
         <v>258</v>
       </c>
@@ -9641,7 +9646,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" ht="18.75" customHeight="1" spans="1:10">
+    <row r="63" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A63" s="4">
         <v>584</v>
       </c>
@@ -9664,7 +9669,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" ht="18.75" customHeight="1" spans="1:10">
+    <row r="64" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A64" s="4">
         <v>597</v>
       </c>
@@ -9687,7 +9692,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="65" ht="18.75" customHeight="1" spans="1:10">
+    <row r="65" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A65" s="4">
         <v>581</v>
       </c>
@@ -9710,7 +9715,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="66" ht="18.75" customHeight="1" spans="1:10">
+    <row r="66" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A66" s="4">
         <v>575</v>
       </c>
@@ -9733,7 +9738,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" ht="18.75" customHeight="1" spans="1:10">
+    <row r="67" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A67" s="4">
         <v>630</v>
       </c>
@@ -9756,7 +9761,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="68" ht="18.75" customHeight="1" spans="1:10">
+    <row r="68" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A68" s="1">
         <v>352</v>
       </c>
@@ -9779,7 +9784,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="69" ht="18.75" customHeight="1" spans="1:10">
+    <row r="69" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A69" s="4">
         <v>498</v>
       </c>
@@ -9802,7 +9807,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="70" ht="18.75" customHeight="1" spans="1:10">
+    <row r="70" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A70" s="4">
         <v>478</v>
       </c>
@@ -9825,7 +9830,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="71" ht="18.75" customHeight="1" spans="1:10">
+    <row r="71" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A71" s="4">
         <v>496</v>
       </c>
@@ -9848,7 +9853,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="72" ht="18.75" customHeight="1" spans="1:10">
+    <row r="72" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A72" s="4">
         <v>582</v>
       </c>
@@ -9871,7 +9876,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="73" ht="18.75" customHeight="1" spans="1:10">
+    <row r="73" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A73" s="4">
         <v>592</v>
       </c>
@@ -9894,7 +9899,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" ht="18.75" customHeight="1" spans="1:10">
+    <row r="74" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A74" s="4">
         <v>466</v>
       </c>
@@ -9917,7 +9922,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="75" ht="18.75" customHeight="1" spans="1:10">
+    <row r="75" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A75" s="4">
         <v>641</v>
       </c>
@@ -9940,7 +9945,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="76" ht="18.75" customHeight="1" spans="1:10">
+    <row r="76" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A76" s="1">
         <v>82</v>
       </c>
@@ -9963,7 +9968,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="77" ht="18.75" customHeight="1" spans="1:10">
+    <row r="77" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A77" s="4">
         <v>361</v>
       </c>
@@ -9986,7 +9991,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="78" ht="18.75" customHeight="1" spans="1:10">
+    <row r="78" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A78" s="4">
         <v>497</v>
       </c>
@@ -10009,7 +10014,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="79" ht="18.75" customHeight="1" spans="1:10">
+    <row r="79" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A79" s="4">
         <v>420</v>
       </c>
@@ -10032,7 +10037,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="80" ht="18.75" customHeight="1" spans="1:10">
+    <row r="80" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A80" s="4">
         <v>367</v>
       </c>
@@ -10055,7 +10060,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" ht="18.75" customHeight="1" spans="1:10">
+    <row r="81" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A81" s="1">
         <v>355</v>
       </c>
@@ -10078,7 +10083,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="82" ht="18.75" customHeight="1" spans="1:10">
+    <row r="82" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A82" s="1">
         <v>186</v>
       </c>
@@ -10101,7 +10106,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="83" ht="18.75" customHeight="1" spans="1:10">
+    <row r="83" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A83" s="1">
         <v>217</v>
       </c>
@@ -10124,7 +10129,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="84" ht="18.75" customHeight="1" spans="1:10">
+    <row r="84" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A84" s="1">
         <v>354</v>
       </c>
@@ -10147,7 +10152,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="85" ht="18.75" customHeight="1" spans="1:10">
+    <row r="85" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A85" s="4">
         <v>523</v>
       </c>
@@ -10170,7 +10175,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="86" ht="18.75" customHeight="1" spans="1:10">
+    <row r="86" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A86" s="4">
         <v>579</v>
       </c>
@@ -10193,7 +10198,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="87" ht="18.75" customHeight="1" spans="1:10">
+    <row r="87" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A87" s="1">
         <v>215</v>
       </c>
@@ -10216,7 +10221,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="88" ht="18.75" customHeight="1" spans="1:10">
+    <row r="88" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A88" s="4">
         <v>542</v>
       </c>
@@ -10239,7 +10244,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="89" ht="18.75" customHeight="1" spans="1:10">
+    <row r="89" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A89" s="1">
         <v>34</v>
       </c>
@@ -10262,7 +10267,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="90" ht="18.75" customHeight="1" spans="1:10">
+    <row r="90" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A90" s="4">
         <v>595</v>
       </c>
@@ -10285,7 +10290,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="91" ht="18.75" customHeight="1" spans="1:10">
+    <row r="91" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A91" s="4">
         <v>593</v>
       </c>
@@ -10308,7 +10313,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="92" ht="18.75" customHeight="1" spans="1:10">
+    <row r="92" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A92" s="1">
         <v>156</v>
       </c>
@@ -10331,7 +10336,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="93" ht="18.75" customHeight="1" spans="1:10">
+    <row r="93" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A93" s="4">
         <v>491</v>
       </c>
@@ -10354,7 +10359,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="94" ht="18.75" customHeight="1" spans="1:10">
+    <row r="94" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A94" s="4">
         <v>490</v>
       </c>
@@ -10377,7 +10382,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="95" ht="18.75" customHeight="1" spans="1:10">
+    <row r="95" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A95" s="4">
         <v>495</v>
       </c>
@@ -10400,7 +10405,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="96" ht="18.75" customHeight="1" spans="1:10">
+    <row r="96" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A96" s="4">
         <v>504</v>
       </c>
@@ -10423,7 +10428,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="97" ht="18.75" customHeight="1" spans="1:10">
+    <row r="97" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A97" s="1">
         <v>179</v>
       </c>
@@ -10446,7 +10451,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="98" ht="18.75" customHeight="1" spans="1:10">
+    <row r="98" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A98" s="1">
         <v>47</v>
       </c>
@@ -10469,7 +10474,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="99" ht="18.75" customHeight="1" spans="1:10">
+    <row r="99" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A99" s="1">
         <v>272</v>
       </c>
@@ -10492,7 +10497,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="100" ht="18.75" customHeight="1" spans="1:10">
+    <row r="100" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A100" s="4">
         <v>647</v>
       </c>
@@ -10515,7 +10520,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="101" ht="18.75" customHeight="1" spans="1:10">
+    <row r="101" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A101" s="4">
         <v>476</v>
       </c>
@@ -10538,7 +10543,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="102" ht="18.75" customHeight="1" spans="1:10">
+    <row r="102" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A102" s="1">
         <v>356</v>
       </c>
@@ -10561,7 +10566,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="103" ht="18.75" customHeight="1" spans="1:10">
+    <row r="103" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A103" s="1">
         <v>28</v>
       </c>
@@ -10584,7 +10589,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="104" ht="18.75" customHeight="1" spans="1:10">
+    <row r="104" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A104" s="1">
         <v>185</v>
       </c>
@@ -10607,7 +10612,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="105" ht="18.75" customHeight="1" spans="1:10">
+    <row r="105" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A105" s="4">
         <v>628</v>
       </c>
@@ -10630,7 +10635,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="106" ht="18.75" customHeight="1" spans="1:10">
+    <row r="106" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A106" s="1">
         <v>160</v>
       </c>
@@ -10653,7 +10658,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="107" ht="18.75" customHeight="1" spans="1:10">
+    <row r="107" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A107" s="1">
         <v>208</v>
       </c>
@@ -10676,7 +10681,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="108" ht="18.75" customHeight="1" spans="1:10">
+    <row r="108" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A108" s="1">
         <v>46</v>
       </c>
@@ -10699,7 +10704,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="109" ht="18.75" customHeight="1" spans="1:10">
+    <row r="109" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A109" s="1">
         <v>184</v>
       </c>
@@ -10722,7 +10727,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="110" ht="18.75" customHeight="1" spans="1:10">
+    <row r="110" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A110" s="4">
         <v>475</v>
       </c>
@@ -10745,7 +10750,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="111" ht="18.75" customHeight="1" spans="1:10">
+    <row r="111" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A111" s="1">
         <v>27</v>
       </c>
@@ -10768,7 +10773,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="112" ht="18.75" customHeight="1" spans="1:10">
+    <row r="112" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A112" s="4">
         <v>376</v>
       </c>
@@ -10791,7 +10796,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="113" ht="18.75" customHeight="1" spans="1:10">
+    <row r="113" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A113" s="4">
         <v>393</v>
       </c>
@@ -10814,7 +10819,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="114" ht="18.75" customHeight="1" spans="1:10">
+    <row r="114" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A114" s="1">
         <v>197</v>
       </c>
@@ -10837,7 +10842,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="115" ht="18.75" customHeight="1" spans="1:10">
+    <row r="115" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A115" s="1">
         <v>24</v>
       </c>
@@ -10863,7 +10868,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="116" ht="18.75" customHeight="1" spans="1:10">
+    <row r="116" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A116" s="1">
         <v>45</v>
       </c>
@@ -10886,7 +10891,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="117" ht="18.75" customHeight="1" spans="1:10">
+    <row r="117" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A117" s="4">
         <v>404</v>
       </c>
@@ -10909,7 +10914,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="118" ht="18.75" customHeight="1" spans="1:10">
+    <row r="118" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A118" s="1">
         <v>31</v>
       </c>
@@ -10932,7 +10937,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="119" ht="18.75" customHeight="1" spans="1:10">
+    <row r="119" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A119" s="1">
         <v>159</v>
       </c>
@@ -10955,7 +10960,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="120" ht="18.75" customHeight="1" spans="1:10">
+    <row r="120" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A120" s="1">
         <v>154</v>
       </c>
@@ -10978,7 +10983,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="121" ht="18.75" customHeight="1" spans="1:10">
+    <row r="121" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A121" s="1">
         <v>14</v>
       </c>
@@ -11004,7 +11009,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="122" ht="18.75" customHeight="1" spans="1:10">
+    <row r="122" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A122" s="4">
         <v>387</v>
       </c>
@@ -11027,7 +11032,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="123" ht="18.75" customHeight="1" spans="1:10">
+    <row r="123" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A123" s="1">
         <v>190</v>
       </c>
@@ -11050,7 +11055,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="124" ht="18.75" customHeight="1" spans="1:10">
+    <row r="124" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A124" s="4">
         <v>489</v>
       </c>
@@ -11073,7 +11078,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="125" ht="18.75" customHeight="1" spans="1:10">
+    <row r="125" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A125" s="1">
         <v>153</v>
       </c>
@@ -11096,7 +11101,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="126" ht="18.75" customHeight="1" spans="1:10">
+    <row r="126" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A126" s="4">
         <v>375</v>
       </c>
@@ -11119,7 +11124,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="127" ht="18.75" customHeight="1" spans="1:10">
+    <row r="127" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A127" s="1">
         <v>291</v>
       </c>
@@ -11142,7 +11147,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="128" ht="18.75" customHeight="1" spans="1:10">
+    <row r="128" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A128" s="1">
         <v>13</v>
       </c>
@@ -11168,7 +11173,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="129" ht="18.75" customHeight="1" spans="1:10">
+    <row r="129" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A129" s="1">
         <v>257</v>
       </c>
@@ -11191,7 +11196,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="130" ht="18.75" customHeight="1" spans="1:10">
+    <row r="130" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A130" s="1">
         <v>60</v>
       </c>
@@ -11214,7 +11219,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="131" ht="18.75" customHeight="1" spans="1:10">
+    <row r="131" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A131" s="4">
         <v>629</v>
       </c>
@@ -11237,7 +11242,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="132" ht="18.75" customHeight="1" spans="1:10">
+    <row r="132" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A132" s="4">
         <v>389</v>
       </c>
@@ -11260,7 +11265,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="133" ht="18.75" customHeight="1" spans="1:10">
+    <row r="133" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A133" s="1">
         <v>320</v>
       </c>
@@ -11283,7 +11288,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="134" ht="18.75" customHeight="1" spans="1:10">
+    <row r="134" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A134" s="4">
         <v>626</v>
       </c>
@@ -11306,7 +11311,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="135" ht="18.75" customHeight="1" spans="1:10">
+    <row r="135" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A135" s="4">
         <v>573</v>
       </c>
@@ -11329,7 +11334,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="136" ht="18.75" customHeight="1" spans="1:10">
+    <row r="136" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A136" s="1">
         <v>343</v>
       </c>
@@ -11352,7 +11357,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="137" ht="18.75" customHeight="1" spans="1:10">
+    <row r="137" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A137" s="4">
         <v>363</v>
       </c>
@@ -11375,7 +11380,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="138" ht="18.75" customHeight="1" spans="1:10">
+    <row r="138" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A138" s="1">
         <v>289</v>
       </c>
@@ -11398,7 +11403,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="139" ht="18.75" customHeight="1" spans="1:10">
+    <row r="139" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A139" s="4">
         <v>539</v>
       </c>
@@ -11421,7 +11426,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="140" ht="18.75" customHeight="1" spans="1:10">
+    <row r="140" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A140" s="4">
         <v>535</v>
       </c>
@@ -11444,7 +11449,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="141" ht="18.75" customHeight="1" spans="1:10">
+    <row r="141" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A141" s="1">
         <v>145</v>
       </c>
@@ -11467,7 +11472,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="142" ht="18.75" customHeight="1" spans="1:10">
+    <row r="142" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A142" s="1">
         <v>146</v>
       </c>
@@ -11490,7 +11495,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="143" ht="18.75" customHeight="1" spans="1:10">
+    <row r="143" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A143" s="1">
         <v>12</v>
       </c>
@@ -11516,7 +11521,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="144" ht="18.75" customHeight="1" spans="1:10">
+    <row r="144" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A144" s="4">
         <v>600</v>
       </c>
@@ -11539,7 +11544,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="145" ht="18.75" customHeight="1" spans="1:10">
+    <row r="145" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A145" s="1">
         <v>79</v>
       </c>
@@ -11562,7 +11567,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="146" ht="18.75" customHeight="1" spans="1:10">
+    <row r="146" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A146" s="4">
         <v>572</v>
       </c>
@@ -11585,7 +11590,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="147" ht="18.75" customHeight="1" spans="1:10">
+    <row r="147" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A147" s="4">
         <v>541</v>
       </c>
@@ -11608,7 +11613,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="148" ht="18.75" customHeight="1" spans="1:10">
+    <row r="148" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A148" s="4">
         <v>617</v>
       </c>
@@ -11631,7 +11636,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="149" ht="18.75" customHeight="1" spans="1:10">
+    <row r="149" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A149" s="4">
         <v>578</v>
       </c>
@@ -11654,7 +11659,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="150" ht="18.75" customHeight="1" spans="1:10">
+    <row r="150" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A150" s="4">
         <v>514</v>
       </c>
@@ -11677,7 +11682,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="151" ht="18.75" customHeight="1" spans="1:10">
+    <row r="151" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A151" s="1">
         <v>148</v>
       </c>
@@ -11700,7 +11705,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="152" ht="18.75" customHeight="1" spans="1:10">
+    <row r="152" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A152" s="4">
         <v>599</v>
       </c>
@@ -11723,7 +11728,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="153" ht="18.75" customHeight="1" spans="1:10">
+    <row r="153" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A153" s="1">
         <v>255</v>
       </c>
@@ -11746,7 +11751,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="154" ht="18.75" customHeight="1" spans="1:10">
+    <row r="154" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A154" s="1">
         <v>80</v>
       </c>
@@ -11769,7 +11774,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="155" ht="18.75" customHeight="1" spans="1:10">
+    <row r="155" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A155" s="1">
         <v>138</v>
       </c>
@@ -11792,7 +11797,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="156" ht="18.75" customHeight="1" spans="1:10">
+    <row r="156" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A156" s="1">
         <v>149</v>
       </c>
@@ -11815,7 +11820,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="157" ht="18.75" customHeight="1" spans="1:10">
+    <row r="157" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A157" s="1">
         <v>140</v>
       </c>
@@ -11838,7 +11843,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="158" ht="18.75" customHeight="1" spans="1:10">
+    <row r="158" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A158" s="1">
         <v>207</v>
       </c>
@@ -11861,7 +11866,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="159" ht="18.75" customHeight="1" spans="1:10">
+    <row r="159" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A159" s="4">
         <v>613</v>
       </c>
@@ -11884,7 +11889,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="160" ht="18.75" customHeight="1" spans="1:10">
+    <row r="160" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A160" s="4">
         <v>520</v>
       </c>
@@ -11907,7 +11912,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="161" ht="18.75" customHeight="1" spans="1:10">
+    <row r="161" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A161" s="4">
         <v>577</v>
       </c>
@@ -11930,7 +11935,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="162" ht="18.75" customHeight="1" spans="1:10">
+    <row r="162" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A162" s="1">
         <v>139</v>
       </c>
@@ -11953,7 +11958,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="163" ht="18.75" customHeight="1" spans="1:10">
+    <row r="163" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A163" s="4">
         <v>615</v>
       </c>
@@ -11976,7 +11981,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="164" ht="18.75" customHeight="1" spans="1:10">
+    <row r="164" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A164" s="4">
         <v>614</v>
       </c>
@@ -11999,7 +12004,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="165" ht="18.75" customHeight="1" spans="1:10">
+    <row r="165" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A165" s="1">
         <v>81</v>
       </c>
@@ -12022,7 +12027,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="166" ht="18.75" customHeight="1" spans="1:10">
+    <row r="166" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A166" s="1">
         <v>206</v>
       </c>
@@ -12045,7 +12050,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="167" ht="18.75" customHeight="1" spans="1:10">
+    <row r="167" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A167" s="1">
         <v>211</v>
       </c>
@@ -12068,7 +12073,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="168" ht="18.75" customHeight="1" spans="1:10">
+    <row r="168" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A168" s="1">
         <v>213</v>
       </c>
@@ -12091,7 +12096,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="169" ht="18.75" customHeight="1" spans="1:10">
+    <row r="169" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A169" s="1">
         <v>212</v>
       </c>
@@ -12114,7 +12119,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="170" ht="18.75" customHeight="1" spans="1:10">
+    <row r="170" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A170" s="4">
         <v>632</v>
       </c>
@@ -12137,7 +12142,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="171" ht="18.75" customHeight="1" spans="1:10">
+    <row r="171" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A171" s="4">
         <v>364</v>
       </c>
@@ -12160,7 +12165,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="172" ht="18.75" customHeight="1" spans="1:10">
+    <row r="172" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A172" s="1">
         <v>144</v>
       </c>
@@ -12183,7 +12188,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" ht="18.75" customHeight="1" spans="1:10">
+    <row r="173" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A173" s="4">
         <v>605</v>
       </c>
@@ -12206,7 +12211,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="174" ht="18.75" customHeight="1" spans="1:10">
+    <row r="174" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A174" s="4">
         <v>606</v>
       </c>
@@ -12229,7 +12234,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="175" ht="18.75" customHeight="1" spans="1:10">
+    <row r="175" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A175" s="4">
         <v>536</v>
       </c>
@@ -12252,7 +12257,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="176" ht="18.75" customHeight="1" spans="1:10">
+    <row r="176" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A176" s="4">
         <v>537</v>
       </c>
@@ -12275,7 +12280,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="177" ht="18.75" customHeight="1" spans="1:10">
+    <row r="177" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A177" s="4">
         <v>622</v>
       </c>
@@ -12298,7 +12303,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="178" ht="18.75" customHeight="1" spans="1:10">
+    <row r="178" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A178" s="1">
         <v>33</v>
       </c>
@@ -12321,7 +12326,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="179" ht="18.75" customHeight="1" spans="1:10">
+    <row r="179" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A179" s="4">
         <v>623</v>
       </c>
@@ -12344,7 +12349,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="180" ht="18.75" customHeight="1" spans="1:10">
+    <row r="180" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A180" s="4">
         <v>588</v>
       </c>
@@ -12367,7 +12372,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="181" ht="18.75" customHeight="1" spans="1:10">
+    <row r="181" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A181" s="4">
         <v>607</v>
       </c>
@@ -12390,7 +12395,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="182" ht="18.75" customHeight="1" spans="1:10">
+    <row r="182" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -12413,7 +12418,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="183" ht="18.75" customHeight="1" spans="1:10">
+    <row r="183" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A183" s="4">
         <v>631</v>
       </c>
@@ -12436,7 +12441,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="184" ht="18.75" customHeight="1" spans="1:10">
+    <row r="184" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A184" s="4">
         <v>538</v>
       </c>
@@ -12459,7 +12464,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="185" ht="18.75" customHeight="1" spans="1:10">
+    <row r="185" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A185" s="1">
         <v>137</v>
       </c>
@@ -12482,7 +12487,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="186" ht="18.75" customHeight="1" spans="1:10">
+    <row r="186" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A186" s="4">
         <v>646</v>
       </c>
@@ -12503,7 +12508,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="187" ht="18.75" customHeight="1" spans="1:10">
+    <row r="187" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A187" s="1">
         <v>152</v>
       </c>
@@ -12524,7 +12529,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="188" ht="18.75" customHeight="1" spans="1:10">
+    <row r="188" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A188" s="4">
         <v>521</v>
       </c>
@@ -12545,7 +12550,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="189" ht="18.75" customHeight="1" spans="1:10">
+    <row r="189" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A189" s="4">
         <v>374</v>
       </c>
@@ -12566,7 +12571,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="190" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="190" ht="18.75" customHeight="1" spans="1:10">
       <c r="A190" s="4">
         <v>378</v>
       </c>
@@ -12587,7 +12592,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="191" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="191" ht="18.75" customHeight="1" spans="1:10">
       <c r="A191" s="4">
         <v>585</v>
       </c>
@@ -12608,7 +12613,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="192" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="192" ht="18.75" customHeight="1" spans="1:10">
       <c r="A192" s="4">
         <v>477</v>
       </c>
@@ -12625,11 +12630,11 @@
       <c r="H192" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J192" s="9" t="s">
+      <c r="J192" s="12" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="193" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="193" ht="18.75" customHeight="1" spans="1:10">
       <c r="A193" s="4">
         <v>410</v>
       </c>
@@ -12650,7 +12655,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="194" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="194" ht="18.75" customHeight="1" spans="1:10">
       <c r="A194" s="4">
         <v>644</v>
       </c>
@@ -12671,7 +12676,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="195" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="195" ht="18.75" customHeight="1" spans="1:10">
       <c r="A195" s="4">
         <v>596</v>
       </c>
@@ -12692,7 +12697,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="196" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="196" ht="18.75" customHeight="1" spans="1:10">
       <c r="A196" s="1">
         <v>143</v>
       </c>
@@ -12713,7 +12718,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="197" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="197" ht="18.75" customHeight="1" spans="1:10">
       <c r="A197" s="4">
         <v>380</v>
       </c>
@@ -12734,7 +12739,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="198" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="198" ht="18.75" customHeight="1" spans="1:10">
       <c r="A198" s="1">
         <v>191</v>
       </c>
@@ -12755,7 +12760,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="199" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="199" ht="18.75" customHeight="1" spans="1:10">
       <c r="A199" s="4">
         <v>428</v>
       </c>
@@ -12776,7 +12781,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="200" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="200" ht="18.75" customHeight="1" spans="1:10">
       <c r="A200" s="1">
         <v>274</v>
       </c>
@@ -12797,7 +12802,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="201" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="201" ht="18.75" customHeight="1" spans="1:10">
       <c r="A201" s="4">
         <v>357</v>
       </c>
@@ -12818,7 +12823,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="202" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="202" ht="18.75" customHeight="1" spans="1:10">
       <c r="A202" s="1">
         <v>316</v>
       </c>
@@ -12839,7 +12844,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="203" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="203" ht="18.75" customHeight="1" spans="1:10">
       <c r="A203" s="4">
         <v>648</v>
       </c>
@@ -12860,7 +12865,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="204" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="204" ht="18.75" customHeight="1" spans="1:10">
       <c r="A204" s="4">
         <v>571</v>
       </c>
@@ -12881,7 +12886,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="205" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="205" ht="18.75" customHeight="1" spans="1:10">
       <c r="A205" s="4">
         <v>576</v>
       </c>
@@ -12902,7 +12907,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="206" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="206" ht="18.75" customHeight="1" spans="1:10">
       <c r="A206" s="4">
         <v>388</v>
       </c>
@@ -12923,7 +12928,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="207" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="207" ht="18.75" customHeight="1" spans="1:10">
       <c r="A207" s="1">
         <v>10</v>
       </c>
@@ -12947,7 +12952,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="208" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="208" ht="18.75" customHeight="1" spans="1:10">
       <c r="A208" s="1">
         <v>1</v>
       </c>
@@ -12977,7 +12982,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="209" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="209" ht="18.75" customHeight="1" spans="1:10">
       <c r="A209" s="4">
         <v>368</v>
       </c>
@@ -12998,7 +13003,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="210" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="210" ht="18.75" customHeight="1" spans="1:10">
       <c r="A210" s="4">
         <v>382</v>
       </c>
@@ -13019,7 +13024,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="211" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="211" ht="18.75" customHeight="1" spans="1:10">
       <c r="A211" s="1">
         <v>3</v>
       </c>
@@ -13043,7 +13048,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="212" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="212" ht="18.75" customHeight="1" spans="1:10">
       <c r="A212" s="4">
         <v>408</v>
       </c>
@@ -13064,7 +13069,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="213" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="213" ht="18.75" customHeight="1" spans="1:10">
       <c r="A213" s="1">
         <v>182</v>
       </c>
@@ -13085,7 +13090,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="214" ht="18.75" hidden="1" customHeight="1" spans="1:10">
+    <row r="214" ht="18.75" customHeight="1" spans="1:10">
       <c r="A214" s="1">
         <v>115</v>
       </c>
@@ -13106,7 +13111,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="215" ht="18.75" customHeight="1" spans="1:10">
+    <row r="215" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A215" s="1">
         <v>246</v>
       </c>
@@ -13129,7 +13134,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="216" ht="18.75" customHeight="1" spans="1:10">
+    <row r="216" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A216" s="4">
         <v>397</v>
       </c>
@@ -13152,7 +13157,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="217" ht="18.75" customHeight="1" spans="1:10">
+    <row r="217" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A217" s="1">
         <v>57</v>
       </c>
@@ -13175,7 +13180,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="218" ht="18.75" customHeight="1" spans="1:10">
+    <row r="218" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A218" s="4">
         <v>513</v>
       </c>
@@ -13198,7 +13203,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="219" ht="18.75" customHeight="1" spans="1:10">
+    <row r="219" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A219" s="4">
         <v>653</v>
       </c>
@@ -13221,7 +13226,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="220" ht="18.75" customHeight="1" spans="1:10">
+    <row r="220" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A220" s="4">
         <v>482</v>
       </c>
@@ -13244,7 +13249,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="221" ht="18.75" customHeight="1" spans="1:10">
+    <row r="221" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A221" s="1">
         <v>277</v>
       </c>
@@ -13267,7 +13272,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="222" ht="18.75" customHeight="1" spans="1:10">
+    <row r="222" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A222" s="4">
         <v>450</v>
       </c>
@@ -13290,7 +13295,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="223" ht="18.75" customHeight="1" spans="1:10">
+    <row r="223" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A223" s="1">
         <v>19</v>
       </c>
@@ -13316,7 +13321,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="224" ht="18.75" customHeight="1" spans="1:10">
+    <row r="224" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A224" s="1">
         <v>199</v>
       </c>
@@ -13339,7 +13344,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="225" ht="18.75" customHeight="1" spans="1:10">
+    <row r="225" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A225" s="4">
         <v>687</v>
       </c>
@@ -13362,7 +13367,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="226" ht="18.75" customHeight="1" spans="1:10">
+    <row r="226" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A226" s="4">
         <v>719</v>
       </c>
@@ -13385,7 +13390,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="227" ht="18.75" customHeight="1" spans="1:10">
+    <row r="227" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A227" s="1">
         <v>198</v>
       </c>
@@ -13408,7 +13413,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="228" ht="18.75" customHeight="1" spans="1:10">
+    <row r="228" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A228" s="4">
         <v>660</v>
       </c>
@@ -13431,7 +13436,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="229" ht="18.75" customHeight="1" spans="1:10">
+    <row r="229" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A229" s="4">
         <v>720</v>
       </c>
@@ -13454,7 +13459,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="230" ht="18.75" customHeight="1" spans="1:10">
+    <row r="230" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A230" s="4">
         <v>396</v>
       </c>
@@ -13477,7 +13482,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="231" ht="18.75" customHeight="1" spans="1:10">
+    <row r="231" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A231" s="1">
         <v>32</v>
       </c>
@@ -13500,7 +13505,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="232" ht="18.75" customHeight="1" spans="1:10">
+    <row r="232" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A232" s="4">
         <v>483</v>
       </c>
@@ -13523,7 +13528,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="233" ht="18.75" customHeight="1" spans="1:10">
+    <row r="233" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A233" s="4">
         <v>540</v>
       </c>
@@ -13546,7 +13551,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="234" ht="18.75" customHeight="1" spans="1:10">
+    <row r="234" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A234" s="4">
         <v>618</v>
       </c>
@@ -13569,7 +13574,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="235" ht="18.75" customHeight="1" spans="1:10">
+    <row r="235" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A235" s="1">
         <v>39</v>
       </c>
@@ -13592,7 +13597,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="236" ht="18.75" customHeight="1" spans="1:10">
+    <row r="236" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A236" s="1">
         <v>113</v>
       </c>
@@ -13615,7 +13620,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="237" ht="18.75" customHeight="1" spans="1:10">
+    <row r="237" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A237" s="1">
         <v>210</v>
       </c>
@@ -13638,7 +13643,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="238" ht="18.75" customHeight="1" spans="1:10">
+    <row r="238" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A238" s="4">
         <v>429</v>
       </c>
@@ -13661,7 +13666,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="239" ht="18.75" customHeight="1" spans="1:10">
+    <row r="239" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A239" s="4">
         <v>468</v>
       </c>
@@ -13684,7 +13689,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="240" ht="18.75" customHeight="1" spans="1:10">
+    <row r="240" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A240" s="4">
         <v>430</v>
       </c>
@@ -13707,7 +13712,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="241" ht="18.75" customHeight="1" spans="1:10">
+    <row r="241" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A241" s="4">
         <v>650</v>
       </c>
@@ -13730,7 +13735,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="242" ht="18.75" customHeight="1" spans="1:10">
+    <row r="242" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A242" s="4">
         <v>738</v>
       </c>
@@ -13753,7 +13758,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="243" ht="18.75" customHeight="1" spans="1:10">
+    <row r="243" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A243" s="1">
         <v>118</v>
       </c>
@@ -13776,7 +13781,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="244" ht="18.75" customHeight="1" spans="1:10">
+    <row r="244" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A244" s="1">
         <v>327</v>
       </c>
@@ -13799,7 +13804,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="245" ht="18.75" customHeight="1" spans="1:10">
+    <row r="245" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A245" s="1">
         <v>163</v>
       </c>
@@ -13822,7 +13827,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="246" ht="18.75" customHeight="1" spans="1:10">
+    <row r="246" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A246" s="1">
         <v>161</v>
       </c>
@@ -13845,7 +13850,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="247" ht="18.75" customHeight="1" spans="1:10">
+    <row r="247" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A247" s="1">
         <v>108</v>
       </c>
@@ -13868,7 +13873,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="248" ht="18.75" customHeight="1" spans="1:10">
+    <row r="248" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A248" s="4">
         <v>686</v>
       </c>
@@ -13891,7 +13896,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="249" ht="18.75" customHeight="1" spans="1:10">
+    <row r="249" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A249" s="1">
         <v>63</v>
       </c>
@@ -13914,7 +13919,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="250" ht="18.75" customHeight="1" spans="1:10">
+    <row r="250" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A250" s="1">
         <v>62</v>
       </c>
@@ -13937,7 +13942,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="251" ht="18.75" customHeight="1" spans="1:10">
+    <row r="251" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A251" s="1">
         <v>102</v>
       </c>
@@ -13960,7 +13965,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="252" ht="18.75" customHeight="1" spans="1:10">
+    <row r="252" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A252" s="1">
         <v>64</v>
       </c>
@@ -13983,7 +13988,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="253" ht="18.75" customHeight="1" spans="1:10">
+    <row r="253" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A253" s="1">
         <v>101</v>
       </c>
@@ -14006,7 +14011,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="254" ht="18.75" customHeight="1" spans="1:10">
+    <row r="254" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A254" s="4">
         <v>501</v>
       </c>
@@ -14029,7 +14034,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="255" ht="18.75" customHeight="1" spans="1:10">
+    <row r="255" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A255" s="1">
         <v>50</v>
       </c>
@@ -14052,7 +14057,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="256" ht="18.75" customHeight="1" spans="1:10">
+    <row r="256" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A256" s="1">
         <v>181</v>
       </c>
@@ -14075,7 +14080,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="257" ht="18.75" customHeight="1" spans="1:10">
+    <row r="257" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A257" s="1">
         <v>105</v>
       </c>
@@ -14098,7 +14103,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="258" ht="18.75" customHeight="1" spans="1:10">
+    <row r="258" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A258" s="1">
         <v>254</v>
       </c>
@@ -14121,7 +14126,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="259" ht="18.75" customHeight="1" spans="1:10">
+    <row r="259" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A259" s="1">
         <v>100</v>
       </c>
@@ -14144,7 +14149,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="260" ht="18.75" customHeight="1" spans="1:10">
+    <row r="260" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A260" s="1">
         <v>127</v>
       </c>
@@ -14167,7 +14172,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="261" ht="18.75" customHeight="1" spans="1:10">
+    <row r="261" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A261" s="4">
         <v>609</v>
       </c>
@@ -14190,7 +14195,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="262" ht="18.75" customHeight="1" spans="1:10">
+    <row r="262" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A262" s="1">
         <v>90</v>
       </c>
@@ -14213,7 +14218,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="263" ht="18.75" customHeight="1" spans="1:10">
+    <row r="263" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A263" s="4">
         <v>666</v>
       </c>
@@ -14236,7 +14241,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="264" ht="18.75" customHeight="1" spans="1:10">
+    <row r="264" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A264" s="4">
         <v>627</v>
       </c>
@@ -14259,7 +14264,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="265" ht="18.75" customHeight="1" spans="1:10">
+    <row r="265" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A265" s="1">
         <v>131</v>
       </c>
@@ -14282,7 +14287,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="266" ht="18.75" customHeight="1" spans="1:10">
+    <row r="266" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A266" s="1">
         <v>104</v>
       </c>
@@ -14305,7 +14310,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="267" ht="18.75" customHeight="1" spans="1:10">
+    <row r="267" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A267" s="1">
         <v>132</v>
       </c>
@@ -14328,7 +14333,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="268" ht="18.75" customHeight="1" spans="1:10">
+    <row r="268" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -14351,7 +14356,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="269" ht="18.75" customHeight="1" spans="1:10">
+    <row r="269" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A269" s="1">
         <v>133</v>
       </c>
@@ -14374,7 +14379,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="270" ht="18.75" customHeight="1" spans="1:10">
+    <row r="270" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A270" s="4">
         <v>651</v>
       </c>
@@ -14397,7 +14402,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="271" ht="18.75" customHeight="1" spans="1:10">
+    <row r="271" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A271" s="1">
         <v>314</v>
       </c>
@@ -14420,7 +14425,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="272" ht="18.75" customHeight="1" spans="1:10">
+    <row r="272" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A272" s="4">
         <v>445</v>
       </c>
@@ -14443,7 +14448,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="273" ht="18.75" customHeight="1" spans="1:10">
+    <row r="273" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A273" s="1">
         <v>203</v>
       </c>
@@ -14466,7 +14471,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="274" ht="18.75" customHeight="1" spans="1:10">
+    <row r="274" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A274" s="4">
         <v>446</v>
       </c>
@@ -14489,7 +14494,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="275" ht="18.75" customHeight="1" spans="1:10">
+    <row r="275" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A275" s="1">
         <v>256</v>
       </c>
@@ -14512,7 +14517,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="276" ht="18.75" customHeight="1" spans="1:10">
+    <row r="276" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A276" s="1">
         <v>134</v>
       </c>
@@ -14535,7 +14540,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="277" ht="18.75" customHeight="1" spans="1:10">
+    <row r="277" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A277" s="4">
         <v>467</v>
       </c>
@@ -14558,7 +14563,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="278" ht="18.75" customHeight="1" spans="1:10">
+    <row r="278" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A278" s="1">
         <v>125</v>
       </c>
@@ -14581,7 +14586,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="279" ht="18.75" customHeight="1" spans="1:10">
+    <row r="279" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A279" s="4">
         <v>503</v>
       </c>
@@ -14604,7 +14609,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="280" ht="18.75" customHeight="1" spans="1:10">
+    <row r="280" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A280" s="4">
         <v>462</v>
       </c>
@@ -14627,7 +14632,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="281" ht="18.75" customHeight="1" spans="1:10">
+    <row r="281" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A281" s="4">
         <v>534</v>
       </c>
@@ -14650,7 +14655,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="282" ht="18.75" customHeight="1" spans="1:10">
+    <row r="282" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A282" s="4">
         <v>532</v>
       </c>
@@ -14673,7 +14678,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="283" ht="18.75" customHeight="1" spans="1:10">
+    <row r="283" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A283" s="1">
         <v>173</v>
       </c>
@@ -14696,7 +14701,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="284" ht="18.75" customHeight="1" spans="1:10">
+    <row r="284" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A284" s="1">
         <v>164</v>
       </c>
@@ -14719,7 +14724,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="285" ht="18.75" customHeight="1" spans="1:10">
+    <row r="285" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A285" s="1">
         <v>168</v>
       </c>
@@ -14742,7 +14747,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="286" ht="18.75" customHeight="1" spans="1:10">
+    <row r="286" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A286" s="4">
         <v>437</v>
       </c>
@@ -14765,7 +14770,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="287" ht="18.75" customHeight="1" spans="1:10">
+    <row r="287" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A287" s="4">
         <v>365</v>
       </c>
@@ -14788,7 +14793,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="288" ht="18.75" customHeight="1" spans="1:10">
+    <row r="288" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A288" s="4">
         <v>509</v>
       </c>
@@ -14811,7 +14816,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="289" ht="18.75" customHeight="1" spans="1:10">
+    <row r="289" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A289" s="1">
         <v>92</v>
       </c>
@@ -14834,7 +14839,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="290" ht="18.75" customHeight="1" spans="1:10">
+    <row r="290" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A290" s="4">
         <v>360</v>
       </c>
@@ -14857,7 +14862,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="291" ht="18.75" customHeight="1" spans="1:10">
+    <row r="291" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A291" s="1">
         <v>93</v>
       </c>
@@ -14880,7 +14885,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="292" ht="18.75" customHeight="1" spans="1:10">
+    <row r="292" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A292" s="1">
         <v>270</v>
       </c>
@@ -14903,7 +14908,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="293" ht="18.75" customHeight="1" spans="1:10">
+    <row r="293" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A293" s="1">
         <v>195</v>
       </c>
@@ -14926,7 +14931,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="294" ht="18.75" customHeight="1" spans="1:10">
+    <row r="294" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A294" s="1">
         <v>157</v>
       </c>
@@ -14949,7 +14954,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="295" ht="18.75" customHeight="1" spans="1:10">
+    <row r="295" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A295" s="1">
         <v>239</v>
       </c>
@@ -14972,7 +14977,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="296" ht="18.75" customHeight="1" spans="1:10">
+    <row r="296" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A296" s="1">
         <v>69</v>
       </c>
@@ -14995,7 +15000,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="297" ht="18.75" customHeight="1" spans="1:10">
+    <row r="297" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A297" s="1">
         <v>240</v>
       </c>
@@ -15018,7 +15023,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="298" ht="18.75" customHeight="1" spans="1:10">
+    <row r="298" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A298" s="1">
         <v>126</v>
       </c>
@@ -15041,7 +15046,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="299" ht="18.75" customHeight="1" spans="1:10">
+    <row r="299" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A299" s="1">
         <v>218</v>
       </c>
@@ -15064,7 +15069,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="300" ht="18.75" customHeight="1" spans="1:10">
+    <row r="300" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A300" s="4">
         <v>500</v>
       </c>
@@ -15087,7 +15092,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="301" ht="18.75" customHeight="1" spans="1:10">
+    <row r="301" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A301" s="4">
         <v>564</v>
       </c>
@@ -15110,7 +15115,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="302" ht="18.75" customHeight="1" spans="1:10">
+    <row r="302" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A302" s="4">
         <v>461</v>
       </c>
@@ -15133,7 +15138,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="303" ht="18.75" customHeight="1" spans="1:10">
+    <row r="303" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A303" s="1">
         <v>68</v>
       </c>
@@ -15156,7 +15161,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="304" ht="18.75" customHeight="1" spans="1:10">
+    <row r="304" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A304" s="4">
         <v>427</v>
       </c>
@@ -15179,7 +15184,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="305" ht="18.75" customHeight="1" spans="1:10">
+    <row r="305" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A305" s="4">
         <v>447</v>
       </c>
@@ -15202,7 +15207,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="306" ht="18.75" customHeight="1" spans="1:10">
+    <row r="306" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A306" s="4">
         <v>510</v>
       </c>
@@ -15225,7 +15230,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="307" ht="18.75" customHeight="1" spans="1:10">
+    <row r="307" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A307" s="1">
         <v>227</v>
       </c>
@@ -15248,7 +15253,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="308" ht="18.75" customHeight="1" spans="1:10">
+    <row r="308" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A308" s="4">
         <v>460</v>
       </c>
@@ -15271,7 +15276,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="309" ht="18.75" customHeight="1" spans="1:10">
+    <row r="309" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A309" s="4">
         <v>569</v>
       </c>
@@ -15294,7 +15299,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="310" ht="18.75" customHeight="1" spans="1:10">
+    <row r="310" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A310" s="1">
         <v>91</v>
       </c>
@@ -15317,7 +15322,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="311" ht="18.75" customHeight="1" spans="1:10">
+    <row r="311" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A311" s="4">
         <v>563</v>
       </c>
@@ -15340,7 +15345,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="312" ht="18.75" customHeight="1" spans="1:10">
+    <row r="312" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A312" s="1">
         <v>124</v>
       </c>
@@ -15363,7 +15368,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="313" ht="18.75" customHeight="1" spans="1:10">
+    <row r="313" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A313" s="4">
         <v>508</v>
       </c>
@@ -15386,7 +15391,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="314" ht="18.75" customHeight="1" spans="1:10">
+    <row r="314" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A314" s="1">
         <v>87</v>
       </c>
@@ -15409,7 +15414,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="315" ht="18.75" customHeight="1" spans="1:10">
+    <row r="315" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A315" s="1">
         <v>265</v>
       </c>
@@ -15432,7 +15437,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="316" ht="18.75" customHeight="1" spans="1:10">
+    <row r="316" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A316" s="1">
         <v>86</v>
       </c>
@@ -15455,7 +15460,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="317" ht="18.75" customHeight="1" spans="1:10">
+    <row r="317" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A317" s="4">
         <v>730</v>
       </c>
@@ -15478,7 +15483,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="318" ht="18.75" customHeight="1" spans="1:10">
+    <row r="318" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A318" s="4">
         <v>533</v>
       </c>
@@ -15501,7 +15506,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="319" ht="18.75" customHeight="1" spans="1:10">
+    <row r="319" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A319" s="4">
         <v>543</v>
       </c>
@@ -15524,7 +15529,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="320" ht="18.75" customHeight="1" spans="1:10">
+    <row r="320" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A320" s="1">
         <v>233</v>
       </c>
@@ -15547,7 +15552,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="321" ht="18.75" customHeight="1" spans="1:10">
+    <row r="321" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A321" s="4">
         <v>395</v>
       </c>
@@ -15570,7 +15575,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="322" ht="18.75" customHeight="1" spans="1:10">
+    <row r="322" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A322" s="1">
         <v>117</v>
       </c>
@@ -15593,7 +15598,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="323" ht="18.75" customHeight="1" spans="1:10">
+    <row r="323" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A323" s="4">
         <v>403</v>
       </c>
@@ -15616,7 +15621,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="324" ht="18.75" customHeight="1" spans="1:10">
+    <row r="324" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A324" s="1">
         <v>333</v>
       </c>
@@ -15639,7 +15644,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="325" ht="18.75" customHeight="1" spans="1:10">
+    <row r="325" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A325" s="1">
         <v>141</v>
       </c>
@@ -15662,7 +15667,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="326" ht="18.75" customHeight="1" spans="1:10">
+    <row r="326" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A326" s="4">
         <v>416</v>
       </c>
@@ -15685,7 +15690,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="327" ht="18.75" customHeight="1" spans="1:10">
+    <row r="327" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A327" s="1">
         <v>72</v>
       </c>
@@ -15708,7 +15713,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="328" ht="18.75" customHeight="1" spans="1:10">
+    <row r="328" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A328" s="4">
         <v>453</v>
       </c>
@@ -15731,7 +15736,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="329" ht="18.75" customHeight="1" spans="1:10">
+    <row r="329" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A329" s="1">
         <v>264</v>
       </c>
@@ -15754,7 +15759,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="330" ht="18.75" customHeight="1" spans="1:10">
+    <row r="330" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A330" s="1">
         <v>9</v>
       </c>
@@ -15780,7 +15785,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="331" ht="18.75" customHeight="1" spans="1:10">
+    <row r="331" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A331" s="4">
         <v>712</v>
       </c>
@@ -15803,7 +15808,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="332" ht="18.75" customHeight="1" spans="1:10">
+    <row r="332" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A332" s="1">
         <v>55</v>
       </c>
@@ -15826,7 +15831,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="333" ht="18.75" customHeight="1" spans="1:10">
+    <row r="333" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A333" s="4">
         <v>590</v>
       </c>
@@ -15849,7 +15854,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="334" ht="18.75" customHeight="1" spans="1:10">
+    <row r="334" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A334" s="1">
         <v>99</v>
       </c>
@@ -15872,7 +15877,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="335" ht="18.75" customHeight="1" spans="1:10">
+    <row r="335" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -15895,7 +15900,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="336" ht="18.75" customHeight="1" spans="1:10">
+    <row r="336" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A336" s="1">
         <v>23</v>
       </c>
@@ -15921,7 +15926,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="337" ht="18.75" customHeight="1" spans="1:10">
+    <row r="337" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A337" s="4">
         <v>635</v>
       </c>
@@ -15944,7 +15949,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="338" ht="18.75" customHeight="1" spans="1:10">
+    <row r="338" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A338" s="4">
         <v>608</v>
       </c>
@@ -15967,7 +15972,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="339" ht="18.75" customHeight="1" spans="1:10">
+    <row r="339" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A339" s="4">
         <v>454</v>
       </c>
@@ -15990,7 +15995,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="340" ht="18.75" customHeight="1" spans="1:10">
+    <row r="340" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A340" s="1">
         <v>151</v>
       </c>
@@ -16013,7 +16018,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="341" ht="18.75" customHeight="1" spans="1:10">
+    <row r="341" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A341" s="1">
         <v>313</v>
       </c>
@@ -16036,7 +16041,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="342" ht="18.75" customHeight="1" spans="1:10">
+    <row r="342" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A342" s="1">
         <v>97</v>
       </c>
@@ -16059,7 +16064,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="343" ht="18.75" customHeight="1" spans="1:10">
+    <row r="343" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A343" s="1">
         <v>219</v>
       </c>
@@ -16082,7 +16087,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="344" ht="18.75" customHeight="1" spans="1:10">
+    <row r="344" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A344" s="1">
         <v>344</v>
       </c>
@@ -16105,7 +16110,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="345" ht="18.75" customHeight="1" spans="1:10">
+    <row r="345" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A345" s="1">
         <v>351</v>
       </c>
@@ -16128,7 +16133,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="346" ht="18.75" customHeight="1" spans="1:10">
+    <row r="346" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A346" s="1">
         <v>266</v>
       </c>
@@ -16151,7 +16156,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="347" ht="18.75" customHeight="1" spans="1:10">
+    <row r="347" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A347" s="1">
         <v>269</v>
       </c>
@@ -16174,7 +16179,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="348" ht="18.75" customHeight="1" spans="1:10">
+    <row r="348" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A348" s="1">
         <v>73</v>
       </c>
@@ -16197,7 +16202,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="349" ht="18.75" customHeight="1" spans="1:10">
+    <row r="349" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A349" s="1">
         <v>22</v>
       </c>
@@ -16223,7 +16228,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="350" ht="18.75" customHeight="1" spans="1:10">
+    <row r="350" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A350" s="1">
         <v>8</v>
       </c>
@@ -16249,7 +16254,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="351" ht="18.75" customHeight="1" spans="1:10">
+    <row r="351" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A351" s="4">
         <v>451</v>
       </c>
@@ -16272,7 +16277,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="352" ht="18.75" customHeight="1" spans="1:10">
+    <row r="352" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A352" s="4">
         <v>494</v>
       </c>
@@ -16295,7 +16300,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="353" ht="18.75" customHeight="1" spans="1:10">
+    <row r="353" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A353" s="1">
         <v>335</v>
       </c>
@@ -16318,7 +16323,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="354" ht="18.75" customHeight="1" spans="1:10">
+    <row r="354" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A354" s="4">
         <v>452</v>
       </c>
@@ -16341,7 +16346,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="355" ht="18.75" customHeight="1" spans="1:10">
+    <row r="355" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A355" s="1">
         <v>7</v>
       </c>
@@ -16367,7 +16372,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="356" ht="18.75" customHeight="1" spans="1:10">
+    <row r="356" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A356" s="1">
         <v>98</v>
       </c>
@@ -16390,7 +16395,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="357" ht="18.75" customHeight="1" spans="1:10">
+    <row r="357" ht="18.75" hidden="1" customHeight="1" spans="1:10">
       <c r="A357" s="4">
         <v>502</v>
       </c>
@@ -16413,7 +16418,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="358" customHeight="1" spans="1:10">
+    <row r="358" hidden="1" customHeight="1" spans="1:10">
       <c r="A358" s="1">
         <v>231</v>
       </c>
@@ -16436,7 +16441,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="359" customHeight="1" spans="1:10">
+    <row r="359" hidden="1" customHeight="1" spans="1:10">
       <c r="A359" s="1">
         <v>150</v>
       </c>
@@ -16459,7 +16464,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="360" customHeight="1" spans="1:10">
+    <row r="360" hidden="1" customHeight="1" spans="1:10">
       <c r="A360" s="4">
         <v>567</v>
       </c>
@@ -16482,7 +16487,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="361" customHeight="1" spans="1:10">
+    <row r="361" hidden="1" customHeight="1" spans="1:10">
       <c r="A361" s="1">
         <v>89</v>
       </c>
@@ -16505,7 +16510,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="362" customHeight="1" spans="1:10">
+    <row r="362" hidden="1" customHeight="1" spans="1:10">
       <c r="A362" s="1">
         <v>88</v>
       </c>
@@ -16528,7 +16533,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="363" customHeight="1" spans="1:10">
+    <row r="363" hidden="1" customHeight="1" spans="1:10">
       <c r="A363" s="1">
         <v>223</v>
       </c>
@@ -16551,7 +16556,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="364" customHeight="1" spans="1:10">
+    <row r="364" hidden="1" customHeight="1" spans="1:10">
       <c r="A364" s="4">
         <v>637</v>
       </c>
@@ -16574,7 +16579,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="365" customHeight="1" spans="1:10">
+    <row r="365" hidden="1" customHeight="1" spans="1:10">
       <c r="A365" s="1">
         <v>6</v>
       </c>
@@ -16600,7 +16605,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="366" customHeight="1" spans="1:10">
+    <row r="366" hidden="1" customHeight="1" spans="1:10">
       <c r="A366" s="1">
         <v>221</v>
       </c>
@@ -16623,7 +16628,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="367" customHeight="1" spans="1:10">
+    <row r="367" hidden="1" customHeight="1" spans="1:10">
       <c r="A367" s="1">
         <v>348</v>
       </c>
@@ -16646,7 +16651,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="368" customHeight="1" spans="1:10">
+    <row r="368" hidden="1" customHeight="1" spans="1:10">
       <c r="A368" s="1">
         <v>331</v>
       </c>
@@ -16669,7 +16674,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="369" customHeight="1" spans="1:10">
+    <row r="369" hidden="1" customHeight="1" spans="1:10">
       <c r="A369" s="1">
         <v>130</v>
       </c>
@@ -16692,7 +16697,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="370" customHeight="1" spans="1:10">
+    <row r="370" hidden="1" customHeight="1" spans="1:10">
       <c r="A370" s="1">
         <v>78</v>
       </c>
@@ -16715,7 +16720,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="371" customHeight="1" spans="1:10">
+    <row r="371" hidden="1" customHeight="1" spans="1:10">
       <c r="A371" s="1">
         <v>172</v>
       </c>
@@ -16738,7 +16743,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="372" customHeight="1" spans="1:10">
+    <row r="372" hidden="1" customHeight="1" spans="1:10">
       <c r="A372" s="1">
         <v>247</v>
       </c>
@@ -16761,7 +16766,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="373" customHeight="1" spans="1:10">
+    <row r="373" hidden="1" customHeight="1" spans="1:10">
       <c r="A373" s="4">
         <v>568</v>
       </c>
@@ -16784,7 +16789,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="374" customHeight="1" spans="1:10">
+    <row r="374" hidden="1" customHeight="1" spans="1:10">
       <c r="A374" s="4">
         <v>562</v>
       </c>
@@ -16807,7 +16812,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="375" customHeight="1" spans="1:10">
+    <row r="375" hidden="1" customHeight="1" spans="1:10">
       <c r="A375" s="4">
         <v>456</v>
       </c>
@@ -16830,7 +16835,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="376" customHeight="1" spans="1:10">
+    <row r="376" hidden="1" customHeight="1" spans="1:10">
       <c r="A376" s="1">
         <v>54</v>
       </c>
@@ -16853,7 +16858,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="377" customHeight="1" spans="1:10">
+    <row r="377" hidden="1" customHeight="1" spans="1:10">
       <c r="A377" s="1">
         <v>349</v>
       </c>
@@ -16876,7 +16881,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="378" customHeight="1" spans="1:10">
+    <row r="378" hidden="1" customHeight="1" spans="1:10">
       <c r="A378" s="1">
         <v>74</v>
       </c>
@@ -16899,7 +16904,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="379" customHeight="1" spans="1:10">
+    <row r="379" hidden="1" customHeight="1" spans="1:10">
       <c r="A379" s="1">
         <v>350</v>
       </c>
@@ -16922,7 +16927,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="380" customHeight="1" spans="1:10">
+    <row r="380" hidden="1" customHeight="1" spans="1:10">
       <c r="A380" s="1">
         <v>288</v>
       </c>
@@ -16945,7 +16950,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="381" customHeight="1" spans="1:10">
+    <row r="381" hidden="1" customHeight="1" spans="1:10">
       <c r="A381" s="1">
         <v>232</v>
       </c>
@@ -16968,7 +16973,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="382" customHeight="1" spans="1:10">
+    <row r="382" hidden="1" customHeight="1" spans="1:10">
       <c r="A382" s="1">
         <v>326</v>
       </c>
@@ -16991,7 +16996,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="383" customHeight="1" spans="1:10">
+    <row r="383" hidden="1" customHeight="1" spans="1:10">
       <c r="A383" s="4">
         <v>636</v>
       </c>
@@ -17014,7 +17019,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="384" customHeight="1" spans="1:10">
+    <row r="384" hidden="1" customHeight="1" spans="1:10">
       <c r="A384" s="4">
         <v>407</v>
       </c>
@@ -17037,7 +17042,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="385" customHeight="1" spans="1:10">
+    <row r="385" hidden="1" customHeight="1" spans="1:10">
       <c r="A385" s="4">
         <v>401</v>
       </c>
@@ -17060,7 +17065,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="386" customHeight="1" spans="1:10">
+    <row r="386" hidden="1" customHeight="1" spans="1:10">
       <c r="A386" s="4">
         <v>400</v>
       </c>
@@ -17083,7 +17088,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="387" customHeight="1" spans="1:10">
+    <row r="387" hidden="1" customHeight="1" spans="1:10">
       <c r="A387" s="4">
         <v>602</v>
       </c>
@@ -17106,7 +17111,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="388" customHeight="1" spans="1:10">
+    <row r="388" hidden="1" customHeight="1" spans="1:10">
       <c r="A388" s="1">
         <v>41</v>
       </c>
@@ -17129,7 +17134,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="389" customHeight="1" spans="1:10">
+    <row r="389" hidden="1" customHeight="1" spans="1:10">
       <c r="A389" s="1">
         <v>340</v>
       </c>
@@ -17152,7 +17157,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="390" customHeight="1" spans="1:10">
+    <row r="390" hidden="1" customHeight="1" spans="1:10">
       <c r="A390" s="1">
         <v>96</v>
       </c>
@@ -17175,7 +17180,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="391" customHeight="1" spans="1:10">
+    <row r="391" hidden="1" customHeight="1" spans="1:10">
       <c r="A391" s="4">
         <v>574</v>
       </c>
@@ -17198,7 +17203,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="392" customHeight="1" spans="1:10">
+    <row r="392" hidden="1" customHeight="1" spans="1:10">
       <c r="A392" s="1">
         <v>52</v>
       </c>
@@ -17221,7 +17226,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="393" customHeight="1" spans="1:10">
+    <row r="393" hidden="1" customHeight="1" spans="1:10">
       <c r="A393" s="1">
         <v>51</v>
       </c>
@@ -17244,7 +17249,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="394" customHeight="1" spans="1:10">
+    <row r="394" hidden="1" customHeight="1" spans="1:10">
       <c r="A394" s="1">
         <v>276</v>
       </c>
@@ -17267,7 +17272,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="395" customHeight="1" spans="1:10">
+    <row r="395" hidden="1" customHeight="1" spans="1:10">
       <c r="A395" s="4">
         <v>442</v>
       </c>
@@ -17290,7 +17295,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="396" customHeight="1" spans="1:10">
+    <row r="396" hidden="1" customHeight="1" spans="1:10">
       <c r="A396" s="1">
         <v>178</v>
       </c>
@@ -17313,7 +17318,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="397" customHeight="1" spans="1:10">
+    <row r="397" hidden="1" customHeight="1" spans="1:10">
       <c r="A397" s="1">
         <v>307</v>
       </c>
@@ -17336,7 +17341,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="398" customHeight="1" spans="1:10">
+    <row r="398" hidden="1" customHeight="1" spans="1:10">
       <c r="A398" s="1">
         <v>339</v>
       </c>
@@ -17359,7 +17364,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="399" customHeight="1" spans="1:10">
+    <row r="399" hidden="1" customHeight="1" spans="1:10">
       <c r="A399" s="1">
         <v>228</v>
       </c>
@@ -17382,7 +17387,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="400" customHeight="1" spans="1:10">
+    <row r="400" hidden="1" customHeight="1" spans="1:10">
       <c r="A400" s="1">
         <v>70</v>
       </c>
@@ -17405,7 +17410,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="401" customHeight="1" spans="1:10">
+    <row r="401" hidden="1" customHeight="1" spans="1:10">
       <c r="A401" s="1">
         <v>77</v>
       </c>
@@ -17428,7 +17433,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="402" customHeight="1" spans="1:10">
+    <row r="402" hidden="1" customHeight="1" spans="1:10">
       <c r="A402" s="1">
         <v>234</v>
       </c>
@@ -17451,7 +17456,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="403" customHeight="1" spans="1:10">
+    <row r="403" hidden="1" customHeight="1" spans="1:10">
       <c r="A403" s="1">
         <v>345</v>
       </c>
@@ -17474,7 +17479,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="404" customHeight="1" spans="1:10">
+    <row r="404" hidden="1" customHeight="1" spans="1:10">
       <c r="A404" s="1">
         <v>26</v>
       </c>
@@ -17497,7 +17502,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="405" customHeight="1" spans="1:10">
+    <row r="405" hidden="1" customHeight="1" spans="1:10">
       <c r="A405" s="1">
         <v>236</v>
       </c>
@@ -17520,7 +17525,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="406" customHeight="1" spans="1:10">
+    <row r="406" hidden="1" customHeight="1" spans="1:10">
       <c r="A406" s="1">
         <v>94</v>
       </c>
@@ -17543,7 +17548,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="407" customHeight="1" spans="1:10">
+    <row r="407" hidden="1" customHeight="1" spans="1:10">
       <c r="A407" s="1">
         <v>71</v>
       </c>
@@ -17566,7 +17571,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="408" customHeight="1" spans="1:10">
+    <row r="408" hidden="1" customHeight="1" spans="1:10">
       <c r="A408" s="4">
         <v>457</v>
       </c>
@@ -17589,7 +17594,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="409" customHeight="1" spans="1:10">
+    <row r="409" hidden="1" customHeight="1" spans="1:10">
       <c r="A409" s="4">
         <v>560</v>
       </c>
@@ -17612,7 +17617,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="410" customHeight="1" spans="1:10">
+    <row r="410" hidden="1" customHeight="1" spans="1:10">
       <c r="A410" s="1">
         <v>49</v>
       </c>
@@ -17635,7 +17640,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="411" customHeight="1" spans="1:10">
+    <row r="411" hidden="1" customHeight="1" spans="1:10">
       <c r="A411" s="1">
         <v>238</v>
       </c>
@@ -17658,7 +17663,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="412" customHeight="1" spans="1:10">
+    <row r="412" hidden="1" customHeight="1" spans="1:10">
       <c r="A412" s="4">
         <v>706</v>
       </c>
@@ -17681,7 +17686,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="413" customHeight="1" spans="1:10">
+    <row r="413" hidden="1" customHeight="1" spans="1:10">
       <c r="A413" s="1">
         <v>129</v>
       </c>
@@ -17704,7 +17709,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="414" customHeight="1" spans="1:10">
+    <row r="414" hidden="1" customHeight="1" spans="1:10">
       <c r="A414" s="4">
         <v>441</v>
       </c>
@@ -17727,7 +17732,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="415" customHeight="1" spans="1:10">
+    <row r="415" hidden="1" customHeight="1" spans="1:10">
       <c r="A415" s="4">
         <v>386</v>
       </c>
@@ -17750,7 +17755,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="416" customHeight="1" spans="1:10">
+    <row r="416" hidden="1" customHeight="1" spans="1:10">
       <c r="A416" s="4">
         <v>439</v>
       </c>
@@ -17773,7 +17778,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="417" customHeight="1" spans="1:10">
+    <row r="417" hidden="1" customHeight="1" spans="1:10">
       <c r="A417" s="4">
         <v>717</v>
       </c>
@@ -17796,7 +17801,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="418" customHeight="1" spans="1:10">
+    <row r="418" hidden="1" customHeight="1" spans="1:10">
       <c r="A418" s="1">
         <v>235</v>
       </c>
@@ -17819,7 +17824,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="419" customHeight="1" spans="1:10">
+    <row r="419" hidden="1" customHeight="1" spans="1:10">
       <c r="A419" s="1">
         <v>95</v>
       </c>
@@ -17842,7 +17847,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="420" customHeight="1" spans="1:10">
+    <row r="420" hidden="1" customHeight="1" spans="1:10">
       <c r="A420" s="4">
         <v>399</v>
       </c>
@@ -17865,7 +17870,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="421" customHeight="1" spans="1:10">
+    <row r="421" hidden="1" customHeight="1" spans="1:10">
       <c r="A421" s="1">
         <v>338</v>
       </c>
@@ -17888,7 +17893,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="422" customHeight="1" spans="1:10">
+    <row r="422" hidden="1" customHeight="1" spans="1:10">
       <c r="A422" s="4">
         <v>518</v>
       </c>
@@ -17911,7 +17916,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="423" customHeight="1" spans="1:10">
+    <row r="423" hidden="1" customHeight="1" spans="1:10">
       <c r="A423" s="4">
         <v>625</v>
       </c>
@@ -17934,7 +17939,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="424" customHeight="1" spans="1:10">
+    <row r="424" hidden="1" customHeight="1" spans="1:10">
       <c r="A424" s="4">
         <v>465</v>
       </c>
@@ -17957,7 +17962,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="425" customHeight="1" spans="1:10">
+    <row r="425" hidden="1" customHeight="1" spans="1:10">
       <c r="A425" s="1">
         <v>38</v>
       </c>
@@ -17980,7 +17985,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="426" customHeight="1" spans="1:10">
+    <row r="426" hidden="1" customHeight="1" spans="1:10">
       <c r="A426" s="4">
         <v>479</v>
       </c>
@@ -18003,7 +18008,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="427" customHeight="1" spans="1:10">
+    <row r="427" hidden="1" customHeight="1" spans="1:10">
       <c r="A427" s="4">
         <v>690</v>
       </c>
@@ -18026,7 +18031,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="428" customHeight="1" spans="1:10">
+    <row r="428" hidden="1" customHeight="1" spans="1:10">
       <c r="A428" s="1">
         <v>220</v>
       </c>
@@ -18049,7 +18054,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="429" customHeight="1" spans="1:10">
+    <row r="429" hidden="1" customHeight="1" spans="1:10">
       <c r="A429" s="4">
         <v>678</v>
       </c>
@@ -18072,7 +18077,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="430" customHeight="1" spans="1:10">
+    <row r="430" hidden="1" customHeight="1" spans="1:10">
       <c r="A430" s="1">
         <v>67</v>
       </c>
@@ -18095,7 +18100,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="431" customHeight="1" spans="1:10">
+    <row r="431" hidden="1" customHeight="1" spans="1:10">
       <c r="A431" s="1">
         <v>123</v>
       </c>
@@ -18118,7 +18123,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="432" customHeight="1" spans="1:10">
+    <row r="432" hidden="1" customHeight="1" spans="1:10">
       <c r="A432" s="1">
         <v>237</v>
       </c>
@@ -18141,7 +18146,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="433" customHeight="1" spans="1:10">
+    <row r="433" hidden="1" customHeight="1" spans="1:10">
       <c r="A433" s="4">
         <v>474</v>
       </c>
@@ -18164,7 +18169,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="434" customHeight="1" spans="1:10">
+    <row r="434" hidden="1" customHeight="1" spans="1:10">
       <c r="A434" s="4">
         <v>734</v>
       </c>
@@ -18187,7 +18192,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="435" customHeight="1" spans="1:10">
+    <row r="435" hidden="1" customHeight="1" spans="1:10">
       <c r="A435" s="4">
         <v>385</v>
       </c>
@@ -18210,7 +18215,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="436" customHeight="1" spans="1:10">
+    <row r="436" hidden="1" customHeight="1" spans="1:10">
       <c r="A436" s="4">
         <v>555</v>
       </c>
@@ -18233,7 +18238,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="437" customHeight="1" spans="1:10">
+    <row r="437" hidden="1" customHeight="1" spans="1:10">
       <c r="A437" s="4">
         <v>471</v>
       </c>
@@ -18256,7 +18261,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="438" customHeight="1" spans="1:10">
+    <row r="438" hidden="1" customHeight="1" spans="1:10">
       <c r="A438" s="1">
         <v>170</v>
       </c>
@@ -18279,7 +18284,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="439" customHeight="1" spans="1:10">
+    <row r="439" hidden="1" customHeight="1" spans="1:10">
       <c r="A439" s="1">
         <v>169</v>
       </c>
@@ -18302,7 +18307,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="440" customHeight="1" spans="1:10">
+    <row r="440" hidden="1" customHeight="1" spans="1:10">
       <c r="A440" s="4">
         <v>695</v>
       </c>
@@ -18325,7 +18330,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="441" customHeight="1" spans="1:10">
+    <row r="441" hidden="1" customHeight="1" spans="1:10">
       <c r="A441" s="1">
         <v>321</v>
       </c>
@@ -18348,7 +18353,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="442" customHeight="1" spans="1:10">
+    <row r="442" hidden="1" customHeight="1" spans="1:10">
       <c r="A442" s="1">
         <v>322</v>
       </c>
@@ -18371,7 +18376,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="443" customHeight="1" spans="1:10">
+    <row r="443" hidden="1" customHeight="1" spans="1:10">
       <c r="A443" s="4">
         <v>528</v>
       </c>
@@ -18394,7 +18399,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="444" customHeight="1" spans="1:10">
+    <row r="444" hidden="1" customHeight="1" spans="1:10">
       <c r="A444" s="1">
         <v>302</v>
       </c>
@@ -18417,7 +18422,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="445" customHeight="1" spans="1:10">
+    <row r="445" hidden="1" customHeight="1" spans="1:10">
       <c r="A445" s="4">
         <v>724</v>
       </c>
@@ -18440,7 +18445,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="446" customHeight="1" spans="1:10">
+    <row r="446" hidden="1" customHeight="1" spans="1:10">
       <c r="A446" s="4">
         <v>402</v>
       </c>
@@ -18463,7 +18468,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="447" customHeight="1" spans="1:10">
+    <row r="447" hidden="1" customHeight="1" spans="1:10">
       <c r="A447" s="1">
         <v>167</v>
       </c>
@@ -18486,7 +18491,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="448" customHeight="1" spans="1:10">
+    <row r="448" hidden="1" customHeight="1" spans="1:10">
       <c r="A448" s="1">
         <v>253</v>
       </c>
@@ -18509,7 +18514,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="449" customHeight="1" spans="1:10">
+    <row r="449" hidden="1" customHeight="1" spans="1:10">
       <c r="A449" s="4">
         <v>718</v>
       </c>
@@ -18532,7 +18537,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="450" customHeight="1" spans="1:10">
+    <row r="450" hidden="1" customHeight="1" spans="1:10">
       <c r="A450" s="1">
         <v>252</v>
       </c>
@@ -18555,7 +18560,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="451" customHeight="1" spans="1:10">
+    <row r="451" hidden="1" customHeight="1" spans="1:10">
       <c r="A451" s="1">
         <v>25</v>
       </c>
@@ -18578,7 +18583,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="452" customHeight="1" spans="1:10">
+    <row r="452" hidden="1" customHeight="1" spans="1:10">
       <c r="A452" s="4">
         <v>425</v>
       </c>
@@ -18601,7 +18606,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="453" customHeight="1" spans="1:10">
+    <row r="453" hidden="1" customHeight="1" spans="1:10">
       <c r="A453" s="1">
         <v>287</v>
       </c>
@@ -18624,7 +18629,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="454" customHeight="1" spans="1:10">
+    <row r="454" hidden="1" customHeight="1" spans="1:10">
       <c r="A454" s="4">
         <v>655</v>
       </c>
@@ -18647,7 +18652,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="455" customHeight="1" spans="1:10">
+    <row r="455" hidden="1" customHeight="1" spans="1:10">
       <c r="A455" s="1">
         <v>76</v>
       </c>
@@ -18670,7 +18675,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="456" customHeight="1" spans="1:10">
+    <row r="456" hidden="1" customHeight="1" spans="1:10">
       <c r="A456" s="1">
         <v>111</v>
       </c>
@@ -18693,7 +18698,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="457" customHeight="1" spans="1:10">
+    <row r="457" hidden="1" customHeight="1" spans="1:10">
       <c r="A457" s="4">
         <v>633</v>
       </c>
@@ -18716,7 +18721,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="458" customHeight="1" spans="1:10">
+    <row r="458" hidden="1" customHeight="1" spans="1:10">
       <c r="A458" s="4">
         <v>700</v>
       </c>
@@ -18739,7 +18744,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="459" customHeight="1" spans="1:10">
+    <row r="459" hidden="1" customHeight="1" spans="1:10">
       <c r="A459" s="1">
         <v>298</v>
       </c>
@@ -18762,7 +18767,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="460" customHeight="1" spans="1:10">
+    <row r="460" hidden="1" customHeight="1" spans="1:10">
       <c r="A460" s="4">
         <v>739</v>
       </c>
@@ -18785,7 +18790,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="461" customHeight="1" spans="1:10">
+    <row r="461" hidden="1" customHeight="1" spans="1:10">
       <c r="A461" s="1">
         <v>325</v>
       </c>
@@ -18808,7 +18813,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="462" customHeight="1" spans="1:10">
+    <row r="462" hidden="1" customHeight="1" spans="1:10">
       <c r="A462" s="1">
         <v>306</v>
       </c>
@@ -18831,7 +18836,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="463" customHeight="1" spans="1:10">
+    <row r="463" hidden="1" customHeight="1" spans="1:10">
       <c r="A463" s="4">
         <v>692</v>
       </c>
@@ -18854,7 +18859,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="464" customHeight="1" spans="1:10">
+    <row r="464" hidden="1" customHeight="1" spans="1:10">
       <c r="A464" s="1">
         <v>263</v>
       </c>
@@ -18877,7 +18882,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="465" customHeight="1" spans="1:10">
+    <row r="465" hidden="1" customHeight="1" spans="1:10">
       <c r="A465" s="4">
         <v>438</v>
       </c>
@@ -18900,7 +18905,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="466" customHeight="1" spans="1:10">
+    <row r="466" hidden="1" customHeight="1" spans="1:10">
       <c r="A466" s="4">
         <v>710</v>
       </c>
@@ -18923,7 +18928,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="467" customHeight="1" spans="1:10">
+    <row r="467" hidden="1" customHeight="1" spans="1:10">
       <c r="A467" s="1">
         <v>11</v>
       </c>
@@ -18949,7 +18954,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="468" customHeight="1" spans="1:10">
+    <row r="468" hidden="1" customHeight="1" spans="1:10">
       <c r="A468" s="4">
         <v>736</v>
       </c>
@@ -18972,7 +18977,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="469" customHeight="1" spans="1:10">
+    <row r="469" hidden="1" customHeight="1" spans="1:10">
       <c r="A469" s="1">
         <v>37</v>
       </c>
@@ -18995,7 +19000,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="470" customHeight="1" spans="1:10">
+    <row r="470" hidden="1" customHeight="1" spans="1:10">
       <c r="A470" s="4">
         <v>559</v>
       </c>
@@ -19018,7 +19023,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="471" customHeight="1" spans="1:10">
+    <row r="471" hidden="1" customHeight="1" spans="1:10">
       <c r="A471" s="4">
         <v>696</v>
       </c>
@@ -19041,7 +19046,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="472" customHeight="1" spans="1:10">
+    <row r="472" hidden="1" customHeight="1" spans="1:10">
       <c r="A472" s="1">
         <v>249</v>
       </c>
@@ -19064,7 +19069,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="473" customHeight="1" spans="1:10">
+    <row r="473" hidden="1" customHeight="1" spans="1:10">
       <c r="A473" s="4">
         <v>553</v>
       </c>
@@ -19087,7 +19092,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="474" customHeight="1" spans="1:10">
+    <row r="474" hidden="1" customHeight="1" spans="1:10">
       <c r="A474" s="4">
         <v>620</v>
       </c>
@@ -19110,7 +19115,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="475" customHeight="1" spans="1:10">
+    <row r="475" hidden="1" customHeight="1" spans="1:10">
       <c r="A475" s="4">
         <v>621</v>
       </c>
@@ -19133,7 +19138,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="476" customHeight="1" spans="1:10">
+    <row r="476" hidden="1" customHeight="1" spans="1:10">
       <c r="A476" s="4">
         <v>619</v>
       </c>
@@ -19156,7 +19161,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="477" customHeight="1" spans="1:10">
+    <row r="477" hidden="1" customHeight="1" spans="1:10">
       <c r="A477" s="1">
         <v>30</v>
       </c>
@@ -19179,7 +19184,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="478" customHeight="1" spans="1:10">
+    <row r="478" hidden="1" customHeight="1" spans="1:10">
       <c r="A478" s="4">
         <v>702</v>
       </c>
@@ -19202,7 +19207,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="479" customHeight="1" spans="1:10">
+    <row r="479" hidden="1" customHeight="1" spans="1:10">
       <c r="A479" s="1">
         <v>294</v>
       </c>
@@ -19225,7 +19230,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="480" customHeight="1" spans="1:10">
+    <row r="480" hidden="1" customHeight="1" spans="1:10">
       <c r="A480" s="4">
         <v>443</v>
       </c>
@@ -19248,7 +19253,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="481" customHeight="1" spans="1:10">
+    <row r="481" hidden="1" customHeight="1" spans="1:10">
       <c r="A481" s="4">
         <v>557</v>
       </c>
@@ -19271,7 +19276,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="482" customHeight="1" spans="1:10">
+    <row r="482" hidden="1" customHeight="1" spans="1:10">
       <c r="A482" s="4">
         <v>459</v>
       </c>
@@ -19294,7 +19299,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="483" customHeight="1" spans="1:10">
+    <row r="483" hidden="1" customHeight="1" spans="1:10">
       <c r="A483" s="1">
         <v>110</v>
       </c>
@@ -19317,7 +19322,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="484" customHeight="1" spans="1:10">
+    <row r="484" hidden="1" customHeight="1" spans="1:10">
       <c r="A484" s="4">
         <v>664</v>
       </c>
@@ -19340,7 +19345,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="485" customHeight="1" spans="1:10">
+    <row r="485" hidden="1" customHeight="1" spans="1:10">
       <c r="A485" s="4">
         <v>697</v>
       </c>
@@ -19363,7 +19368,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="486" customHeight="1" spans="1:10">
+    <row r="486" hidden="1" customHeight="1" spans="1:10">
       <c r="A486" s="1">
         <v>293</v>
       </c>
@@ -19386,7 +19391,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="487" customHeight="1" spans="1:10">
+    <row r="487" hidden="1" customHeight="1" spans="1:10">
       <c r="A487" s="4">
         <v>727</v>
       </c>
@@ -19409,7 +19414,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="488" customHeight="1" spans="1:10">
+    <row r="488" hidden="1" customHeight="1" spans="1:10">
       <c r="A488" s="4">
         <v>680</v>
       </c>
@@ -19432,7 +19437,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="489" customHeight="1" spans="1:10">
+    <row r="489" hidden="1" customHeight="1" spans="1:10">
       <c r="A489" s="4">
         <v>722</v>
       </c>
@@ -19455,7 +19460,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="490" customHeight="1" spans="1:10">
+    <row r="490" hidden="1" customHeight="1" spans="1:10">
       <c r="A490" s="1">
         <v>222</v>
       </c>
@@ -19478,7 +19483,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="491" customHeight="1" spans="1:10">
+    <row r="491" hidden="1" customHeight="1" spans="1:10">
       <c r="A491" s="4">
         <v>693</v>
       </c>
@@ -19501,7 +19506,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="492" customHeight="1" spans="1:10">
+    <row r="492" hidden="1" customHeight="1" spans="1:10">
       <c r="A492" s="4">
         <v>663</v>
       </c>
@@ -19524,7 +19529,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="493" customHeight="1" spans="1:10">
+    <row r="493" hidden="1" customHeight="1" spans="1:10">
       <c r="A493" s="4">
         <v>566</v>
       </c>
@@ -19547,7 +19552,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="494" customHeight="1" spans="1:10">
+    <row r="494" hidden="1" customHeight="1" spans="1:10">
       <c r="A494" s="4">
         <v>486</v>
       </c>
@@ -19570,7 +19575,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="495" customHeight="1" spans="1:10">
+    <row r="495" hidden="1" customHeight="1" spans="1:10">
       <c r="A495" s="4">
         <v>485</v>
       </c>
@@ -19593,7 +19598,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="496" customHeight="1" spans="1:10">
+    <row r="496" hidden="1" customHeight="1" spans="1:10">
       <c r="A496" s="4">
         <v>716</v>
       </c>
@@ -19616,7 +19621,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="497" customHeight="1" spans="1:10">
+    <row r="497" hidden="1" customHeight="1" spans="1:10">
       <c r="A497" s="1">
         <v>312</v>
       </c>
@@ -19639,7 +19644,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="498" customHeight="1" spans="1:10">
+    <row r="498" hidden="1" customHeight="1" spans="1:10">
       <c r="A498" s="1">
         <v>165</v>
       </c>
@@ -19662,7 +19667,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="499" customHeight="1" spans="1:10">
+    <row r="499" hidden="1" customHeight="1" spans="1:10">
       <c r="A499" s="4">
         <v>701</v>
       </c>
@@ -19685,7 +19690,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="500" customHeight="1" spans="1:10">
+    <row r="500" hidden="1" customHeight="1" spans="1:10">
       <c r="A500" s="4">
         <v>679</v>
       </c>
@@ -19708,7 +19713,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="501" customHeight="1" spans="1:10">
+    <row r="501" hidden="1" customHeight="1" spans="1:10">
       <c r="A501" s="4">
         <v>662</v>
       </c>
@@ -19731,7 +19736,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="502" customHeight="1" spans="1:10">
+    <row r="502" hidden="1" customHeight="1" spans="1:10">
       <c r="A502" s="4">
         <v>715</v>
       </c>
@@ -19754,7 +19759,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="503" customHeight="1" spans="1:10">
+    <row r="503" hidden="1" customHeight="1" spans="1:10">
       <c r="A503" s="4">
         <v>688</v>
       </c>
@@ -19777,7 +19782,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="504" customHeight="1" spans="1:10">
+    <row r="504" hidden="1" customHeight="1" spans="1:10">
       <c r="A504" s="1">
         <v>18</v>
       </c>
@@ -19803,7 +19808,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="505" customHeight="1" spans="1:10">
+    <row r="505" hidden="1" customHeight="1" spans="1:10">
       <c r="A505" s="1">
         <v>83</v>
       </c>
@@ -19826,7 +19831,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="506" customHeight="1" spans="1:10">
+    <row r="506" hidden="1" customHeight="1" spans="1:10">
       <c r="A506" s="1">
         <v>323</v>
       </c>
@@ -19849,7 +19854,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="507" customHeight="1" spans="1:10">
+    <row r="507" hidden="1" customHeight="1" spans="1:10">
       <c r="A507" s="1">
         <v>120</v>
       </c>
@@ -19872,7 +19877,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="508" customHeight="1" spans="1:10">
+    <row r="508" hidden="1" customHeight="1" spans="1:10">
       <c r="A508" s="4">
         <v>683</v>
       </c>
@@ -19895,7 +19900,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="509" customHeight="1" spans="1:10">
+    <row r="509" hidden="1" customHeight="1" spans="1:10">
       <c r="A509" s="1">
         <v>304</v>
       </c>
@@ -19918,7 +19923,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="510" customHeight="1" spans="1:10">
+    <row r="510" hidden="1" customHeight="1" spans="1:10">
       <c r="A510" s="1">
         <v>17</v>
       </c>
@@ -19944,7 +19949,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="511" customHeight="1" spans="1:10">
+    <row r="511" hidden="1" customHeight="1" spans="1:10">
       <c r="A511" s="4">
         <v>554</v>
       </c>
@@ -19967,7 +19972,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="512" customHeight="1" spans="1:10">
+    <row r="512" hidden="1" customHeight="1" spans="1:10">
       <c r="A512" s="1">
         <v>121</v>
       </c>
@@ -19990,7 +19995,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="513" customHeight="1" spans="1:10">
+    <row r="513" hidden="1" customHeight="1" spans="1:10">
       <c r="A513" s="4">
         <v>733</v>
       </c>
@@ -20013,7 +20018,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="514" customHeight="1" spans="1:10">
+    <row r="514" hidden="1" customHeight="1" spans="1:10">
       <c r="A514" s="1">
         <v>309</v>
       </c>
@@ -20036,7 +20041,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="515" customHeight="1" spans="1:10">
+    <row r="515" hidden="1" customHeight="1" spans="1:10">
       <c r="A515" s="1">
         <v>171</v>
       </c>
@@ -20059,7 +20064,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="516" customHeight="1" spans="1:10">
+    <row r="516" hidden="1" customHeight="1" spans="1:10">
       <c r="A516" s="4">
         <v>435</v>
       </c>
@@ -20082,7 +20087,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="517" customHeight="1" spans="1:10">
+    <row r="517" hidden="1" customHeight="1" spans="1:10">
       <c r="A517" s="4">
         <v>731</v>
       </c>
@@ -20105,7 +20110,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="518" customHeight="1" spans="1:10">
+    <row r="518" hidden="1" customHeight="1" spans="1:10">
       <c r="A518" s="1">
         <v>330</v>
       </c>
@@ -20128,7 +20133,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="519" customHeight="1" spans="1:10">
+    <row r="519" hidden="1" customHeight="1" spans="1:10">
       <c r="A519" s="1">
         <v>286</v>
       </c>
@@ -20151,7 +20156,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="520" customHeight="1" spans="1:10">
+    <row r="520" hidden="1" customHeight="1" spans="1:10">
       <c r="A520" s="1">
         <v>300</v>
       </c>
@@ -20174,7 +20179,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="521" customHeight="1" spans="1:10">
+    <row r="521" hidden="1" customHeight="1" spans="1:10">
       <c r="A521" s="4">
         <v>480</v>
       </c>
@@ -20197,7 +20202,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="522" customHeight="1" spans="1:10">
+    <row r="522" hidden="1" customHeight="1" spans="1:10">
       <c r="A522" s="4">
         <v>472</v>
       </c>
@@ -20220,7 +20225,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="523" customHeight="1" spans="1:10">
+    <row r="523" hidden="1" customHeight="1" spans="1:10">
       <c r="A523" s="4">
         <v>473</v>
       </c>
@@ -20243,7 +20248,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="524" customHeight="1" spans="1:10">
+    <row r="524" hidden="1" customHeight="1" spans="1:10">
       <c r="A524" s="1">
         <v>147</v>
       </c>
@@ -20266,7 +20271,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="525" customHeight="1" spans="1:10">
+    <row r="525" hidden="1" customHeight="1" spans="1:10">
       <c r="A525" s="4">
         <v>434</v>
       </c>
@@ -20289,7 +20294,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="526" customHeight="1" spans="1:10">
+    <row r="526" hidden="1" customHeight="1" spans="1:10">
       <c r="A526" s="1">
         <v>204</v>
       </c>
@@ -20312,7 +20317,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="527" customHeight="1" spans="1:10">
+    <row r="527" hidden="1" customHeight="1" spans="1:10">
       <c r="A527" s="4">
         <v>469</v>
       </c>
@@ -20335,7 +20340,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="528" customHeight="1" spans="1:10">
+    <row r="528" hidden="1" customHeight="1" spans="1:10">
       <c r="A528" s="1">
         <v>346</v>
       </c>
@@ -20358,7 +20363,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="529" customHeight="1" spans="1:10">
+    <row r="529" hidden="1" customHeight="1" spans="1:10">
       <c r="A529" s="1">
         <v>260</v>
       </c>
@@ -20381,7 +20386,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="530" customHeight="1" spans="1:10">
+    <row r="530" hidden="1" customHeight="1" spans="1:10">
       <c r="A530" s="1">
         <v>109</v>
       </c>
@@ -20404,7 +20409,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="531" customHeight="1" spans="1:10">
+    <row r="531" hidden="1" customHeight="1" spans="1:10">
       <c r="A531" s="4">
         <v>725</v>
       </c>
@@ -20427,7 +20432,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="532" customHeight="1" spans="1:10">
+    <row r="532" hidden="1" customHeight="1" spans="1:10">
       <c r="A532" s="4">
         <v>689</v>
       </c>
@@ -20450,7 +20455,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="533" customHeight="1" spans="1:10">
+    <row r="533" hidden="1" customHeight="1" spans="1:10">
       <c r="A533" s="4">
         <v>527</v>
       </c>
@@ -20473,7 +20478,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="534" customHeight="1" spans="1:10">
+    <row r="534" hidden="1" customHeight="1" spans="1:10">
       <c r="A534" s="4">
         <v>406</v>
       </c>
@@ -20496,7 +20501,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="535" customHeight="1" spans="1:10">
+    <row r="535" hidden="1" customHeight="1" spans="1:10">
       <c r="A535" s="4">
         <v>676</v>
       </c>
@@ -20519,7 +20524,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="536" customHeight="1" spans="1:10">
+    <row r="536" hidden="1" customHeight="1" spans="1:10">
       <c r="A536" s="4">
         <v>723</v>
       </c>
@@ -20542,7 +20547,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="537" customHeight="1" spans="1:10">
+    <row r="537" hidden="1" customHeight="1" spans="1:10">
       <c r="A537" s="4">
         <v>698</v>
       </c>
@@ -20565,7 +20570,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="538" customHeight="1" spans="1:10">
+    <row r="538" hidden="1" customHeight="1" spans="1:10">
       <c r="A538" s="1">
         <v>305</v>
       </c>
@@ -20588,7 +20593,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="539" customHeight="1" spans="1:10">
+    <row r="539" hidden="1" customHeight="1" spans="1:10">
       <c r="A539" s="4">
         <v>412</v>
       </c>
@@ -20611,7 +20616,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="540" customHeight="1" spans="1:10">
+    <row r="540" hidden="1" customHeight="1" spans="1:10">
       <c r="A540" s="1">
         <v>114</v>
       </c>
@@ -20634,7 +20639,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="541" customHeight="1" spans="1:10">
+    <row r="541" hidden="1" customHeight="1" spans="1:10">
       <c r="A541" s="1">
         <v>119</v>
       </c>
@@ -20657,7 +20662,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="542" customHeight="1" spans="1:10">
+    <row r="542" hidden="1" customHeight="1" spans="1:10">
       <c r="A542" s="4">
         <v>624</v>
       </c>
@@ -20680,7 +20685,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="543" customHeight="1" spans="1:10">
+    <row r="543" hidden="1" customHeight="1" spans="1:10">
       <c r="A543" s="1">
         <v>56</v>
       </c>
@@ -20703,7 +20708,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="544" customHeight="1" spans="1:10">
+    <row r="544" hidden="1" customHeight="1" spans="1:10">
       <c r="A544" s="4">
         <v>694</v>
       </c>
@@ -20726,7 +20731,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="545" customHeight="1" spans="1:10">
+    <row r="545" hidden="1" customHeight="1" spans="1:10">
       <c r="A545" s="4">
         <v>705</v>
       </c>
@@ -20749,7 +20754,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="546" customHeight="1" spans="1:10">
+    <row r="546" hidden="1" customHeight="1" spans="1:10">
       <c r="A546" s="4">
         <v>440</v>
       </c>
@@ -20772,7 +20777,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="547" customHeight="1" spans="1:10">
+    <row r="547" hidden="1" customHeight="1" spans="1:10">
       <c r="A547" s="4">
         <v>426</v>
       </c>
@@ -20795,7 +20800,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="548" customHeight="1" spans="1:10">
+    <row r="548" hidden="1" customHeight="1" spans="1:10">
       <c r="A548" s="4">
         <v>741</v>
       </c>
@@ -20818,7 +20823,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="549" customHeight="1" spans="1:10">
+    <row r="549" hidden="1" customHeight="1" spans="1:10">
       <c r="A549" s="4">
         <v>411</v>
       </c>
@@ -20841,7 +20846,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="550" customHeight="1" spans="1:10">
+    <row r="550" hidden="1" customHeight="1" spans="1:10">
       <c r="A550" s="4">
         <v>415</v>
       </c>
@@ -20864,7 +20869,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="551" customHeight="1" spans="1:10">
+    <row r="551" hidden="1" customHeight="1" spans="1:10">
       <c r="A551" s="1">
         <v>299</v>
       </c>
@@ -20887,7 +20892,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="552" customHeight="1" spans="1:10">
+    <row r="552" hidden="1" customHeight="1" spans="1:10">
       <c r="A552" s="4">
         <v>616</v>
       </c>
@@ -20910,7 +20915,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="553" customHeight="1" spans="1:10">
+    <row r="553" hidden="1" customHeight="1" spans="1:10">
       <c r="A553" s="1">
         <v>48</v>
       </c>
@@ -20933,7 +20938,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="554" customHeight="1" spans="1:10">
+    <row r="554" hidden="1" customHeight="1" spans="1:10">
       <c r="A554" s="1">
         <v>53</v>
       </c>
@@ -20956,7 +20961,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="555" customHeight="1" spans="1:10">
+    <row r="555" hidden="1" customHeight="1" spans="1:10">
       <c r="A555" s="1">
         <v>324</v>
       </c>
@@ -20979,7 +20984,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="556" customHeight="1" spans="1:10">
+    <row r="556" hidden="1" customHeight="1" spans="1:10">
       <c r="A556" s="1">
         <v>295</v>
       </c>
@@ -21002,7 +21007,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="557" customHeight="1" spans="1:10">
+    <row r="557" hidden="1" customHeight="1" spans="1:10">
       <c r="A557" s="4">
         <v>433</v>
       </c>
@@ -21025,7 +21030,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="558" customHeight="1" spans="1:10">
+    <row r="558" hidden="1" customHeight="1" spans="1:10">
       <c r="A558" s="1">
         <v>311</v>
       </c>
@@ -21048,7 +21053,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="559" customHeight="1" spans="1:10">
+    <row r="559" hidden="1" customHeight="1" spans="1:10">
       <c r="A559" s="4">
         <v>436</v>
       </c>
@@ -21071,7 +21076,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="560" customHeight="1" spans="1:10">
+    <row r="560" hidden="1" customHeight="1" spans="1:10">
       <c r="A560" s="1">
         <v>308</v>
       </c>
@@ -21094,7 +21099,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="561" customHeight="1" spans="1:10">
+    <row r="561" hidden="1" customHeight="1" spans="1:10">
       <c r="A561" s="1">
         <v>280</v>
       </c>
@@ -21117,7 +21122,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="562" customHeight="1" spans="1:10">
+    <row r="562" hidden="1" customHeight="1" spans="1:10">
       <c r="A562" s="4">
         <v>713</v>
       </c>
@@ -21140,7 +21145,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="563" customHeight="1" spans="1:10">
+    <row r="563" hidden="1" customHeight="1" spans="1:10">
       <c r="A563" s="1">
         <v>261</v>
       </c>
@@ -21163,7 +21168,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="564" customHeight="1" spans="1:10">
+    <row r="564" hidden="1" customHeight="1" spans="1:10">
       <c r="A564" s="1">
         <v>226</v>
       </c>
@@ -21186,7 +21191,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="565" customHeight="1" spans="1:10">
+    <row r="565" hidden="1" customHeight="1" spans="1:10">
       <c r="A565" s="4">
         <v>391</v>
       </c>
@@ -21209,7 +21214,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="566" customHeight="1" spans="1:10">
+    <row r="566" hidden="1" customHeight="1" spans="1:10">
       <c r="A566" s="4">
         <v>658</v>
       </c>
@@ -21232,7 +21237,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="567" customHeight="1" spans="1:10">
+    <row r="567" hidden="1" customHeight="1" spans="1:10">
       <c r="A567" s="4">
         <v>656</v>
       </c>
@@ -21255,7 +21260,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="568" customHeight="1" spans="1:10">
+    <row r="568" hidden="1" customHeight="1" spans="1:10">
       <c r="A568" s="4">
         <v>383</v>
       </c>
@@ -21278,7 +21283,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="569" customHeight="1" spans="1:10">
+    <row r="569" hidden="1" customHeight="1" spans="1:10">
       <c r="A569" s="1">
         <v>59</v>
       </c>
@@ -21301,7 +21306,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="570" customHeight="1" spans="1:10">
+    <row r="570" hidden="1" customHeight="1" spans="1:10">
       <c r="A570" s="1">
         <v>290</v>
       </c>
@@ -21324,7 +21329,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="571" customHeight="1" spans="1:10">
+    <row r="571" hidden="1" customHeight="1" spans="1:10">
       <c r="A571" s="1">
         <v>250</v>
       </c>
@@ -21347,7 +21352,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="572" customHeight="1" spans="1:10">
+    <row r="572" hidden="1" customHeight="1" spans="1:10">
       <c r="A572" s="4">
         <v>703</v>
       </c>
@@ -21370,7 +21375,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="573" customHeight="1" spans="1:10">
+    <row r="573" hidden="1" customHeight="1" spans="1:10">
       <c r="A573" s="4">
         <v>587</v>
       </c>
@@ -21393,7 +21398,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="574" customHeight="1" spans="1:10">
+    <row r="574" hidden="1" customHeight="1" spans="1:10">
       <c r="A574" s="1">
         <v>224</v>
       </c>
@@ -21416,7 +21421,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="575" customHeight="1" spans="1:10">
+    <row r="575" hidden="1" customHeight="1" spans="1:10">
       <c r="A575" s="4">
         <v>458</v>
       </c>
@@ -21439,7 +21444,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="576" customHeight="1" spans="1:10">
+    <row r="576" hidden="1" customHeight="1" spans="1:10">
       <c r="A576" s="4">
         <v>704</v>
       </c>
@@ -21462,7 +21467,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="577" customHeight="1" spans="1:10">
+    <row r="577" hidden="1" customHeight="1" spans="1:10">
       <c r="A577" s="1">
         <v>225</v>
       </c>
@@ -21485,7 +21490,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="578" customHeight="1" spans="1:10">
+    <row r="578" hidden="1" customHeight="1" spans="1:10">
       <c r="A578" s="4">
         <v>711</v>
       </c>
@@ -21508,7 +21513,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="579" customHeight="1" spans="1:10">
+    <row r="579" hidden="1" customHeight="1" spans="1:10">
       <c r="A579" s="1">
         <v>209</v>
       </c>
@@ -21531,7 +21536,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="580" customHeight="1" spans="1:10">
+    <row r="580" hidden="1" customHeight="1" spans="1:10">
       <c r="A580" s="1">
         <v>66</v>
       </c>
@@ -21554,7 +21559,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="581" customHeight="1" spans="1:10">
+    <row r="581" hidden="1" customHeight="1" spans="1:10">
       <c r="A581" s="1">
         <v>336</v>
       </c>
@@ -21577,7 +21582,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="582" customHeight="1" spans="1:10">
+    <row r="582" hidden="1" customHeight="1" spans="1:10">
       <c r="A582" s="1">
         <v>65</v>
       </c>
@@ -21600,7 +21605,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="583" customHeight="1" spans="1:10">
+    <row r="583" hidden="1" customHeight="1" spans="1:10">
       <c r="A583" s="4">
         <v>699</v>
       </c>
@@ -21623,7 +21628,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="584" customHeight="1" spans="1:10">
+    <row r="584" hidden="1" customHeight="1" spans="1:10">
       <c r="A584" s="1">
         <v>248</v>
       </c>
@@ -21646,7 +21651,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="585" customHeight="1" spans="1:10">
+    <row r="585" hidden="1" customHeight="1" spans="1:10">
       <c r="A585" s="1">
         <v>251</v>
       </c>
@@ -21669,7 +21674,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="586" customHeight="1" spans="1:10">
+    <row r="586" hidden="1" customHeight="1" spans="1:10">
       <c r="A586" s="1">
         <v>136</v>
       </c>
@@ -21692,7 +21697,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="587" customHeight="1" spans="1:10">
+    <row r="587" hidden="1" customHeight="1" spans="1:10">
       <c r="A587" s="1">
         <v>107</v>
       </c>
@@ -21715,7 +21720,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="588" customHeight="1" spans="1:10">
+    <row r="588" hidden="1" customHeight="1" spans="1:10">
       <c r="A588" s="1">
         <v>201</v>
       </c>
@@ -21738,7 +21743,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="589" customHeight="1" spans="1:10">
+    <row r="589" hidden="1" customHeight="1" spans="1:10">
       <c r="A589" s="1">
         <v>243</v>
       </c>
@@ -21761,7 +21766,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="590" customHeight="1" spans="1:10">
+    <row r="590" hidden="1" customHeight="1" spans="1:10">
       <c r="A590" s="1">
         <v>297</v>
       </c>
@@ -21784,7 +21789,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="591" customHeight="1" spans="1:10">
+    <row r="591" hidden="1" customHeight="1" spans="1:10">
       <c r="A591" s="1">
         <v>337</v>
       </c>
@@ -21807,7 +21812,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="592" customHeight="1" spans="1:10">
+    <row r="592" hidden="1" customHeight="1" spans="1:10">
       <c r="A592" s="1">
         <v>347</v>
       </c>
@@ -21830,7 +21835,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="593" customHeight="1" spans="1:10">
+    <row r="593" hidden="1" customHeight="1" spans="1:10">
       <c r="A593" s="4">
         <v>682</v>
       </c>
@@ -21853,7 +21858,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="594" customHeight="1" spans="1:10">
+    <row r="594" hidden="1" customHeight="1" spans="1:10">
       <c r="A594" s="1">
         <v>301</v>
       </c>
@@ -21876,7 +21881,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="595" customHeight="1" spans="1:10">
+    <row r="595" hidden="1" customHeight="1" spans="1:10">
       <c r="A595" s="4">
         <v>691</v>
       </c>
@@ -21899,7 +21904,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="596" customHeight="1" spans="1:10">
+    <row r="596" hidden="1" customHeight="1" spans="1:10">
       <c r="A596" s="1">
         <v>278</v>
       </c>
@@ -21922,7 +21927,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="597" customHeight="1" spans="1:10">
+    <row r="597" hidden="1" customHeight="1" spans="1:10">
       <c r="A597" s="1">
         <v>194</v>
       </c>
@@ -21945,7 +21950,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="598" customHeight="1" spans="1:10">
+    <row r="598" hidden="1" customHeight="1" spans="1:10">
       <c r="A598" s="1">
         <v>196</v>
       </c>
@@ -21968,7 +21973,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="599" customHeight="1" spans="1:10">
+    <row r="599" hidden="1" customHeight="1" spans="1:10">
       <c r="A599" s="4">
         <v>681</v>
       </c>
@@ -21991,7 +21996,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="600" customHeight="1" spans="1:10">
+    <row r="600" hidden="1" customHeight="1" spans="1:10">
       <c r="A600" s="4">
         <v>448</v>
       </c>
@@ -22014,7 +22019,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="601" customHeight="1" spans="1:10">
+    <row r="601" hidden="1" customHeight="1" spans="1:10">
       <c r="A601" s="4">
         <v>481</v>
       </c>
@@ -22037,7 +22042,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="602" customHeight="1" spans="1:10">
+    <row r="602" hidden="1" customHeight="1" spans="1:10">
       <c r="A602" s="1">
         <v>75</v>
       </c>
@@ -22060,7 +22065,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="603" customHeight="1" spans="1:10">
+    <row r="603" hidden="1" customHeight="1" spans="1:10">
       <c r="A603" s="4">
         <v>449</v>
       </c>
@@ -22083,7 +22088,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="604" customHeight="1" spans="1:10">
+    <row r="604" hidden="1" customHeight="1" spans="1:10">
       <c r="A604" s="1">
         <v>135</v>
       </c>
@@ -22106,7 +22111,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="605" customHeight="1" spans="1:10">
+    <row r="605" hidden="1" customHeight="1" spans="1:10">
       <c r="A605" s="4">
         <v>721</v>
       </c>
@@ -22129,7 +22134,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="606" customHeight="1" spans="1:10">
+    <row r="606" hidden="1" customHeight="1" spans="1:10">
       <c r="A606" s="4">
         <v>707</v>
       </c>
@@ -22152,7 +22157,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="607" customHeight="1" spans="1:10">
+    <row r="607" hidden="1" customHeight="1" spans="1:10">
       <c r="A607" s="1">
         <v>310</v>
       </c>
@@ -22175,7 +22180,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="608" customHeight="1" spans="1:10">
+    <row r="608" hidden="1" customHeight="1" spans="1:10">
       <c r="A608" s="1">
         <v>230</v>
       </c>
@@ -22198,7 +22203,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="609" customHeight="1" spans="1:10">
+    <row r="609" hidden="1" customHeight="1" spans="1:10">
       <c r="A609" s="1">
         <v>242</v>
       </c>
@@ -22221,7 +22226,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="610" customHeight="1" spans="1:10">
+    <row r="610" hidden="1" customHeight="1" spans="1:10">
       <c r="A610" s="4">
         <v>654</v>
       </c>
@@ -22244,7 +22249,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="611" customHeight="1" spans="1:10">
+    <row r="611" hidden="1" customHeight="1" spans="1:10">
       <c r="A611" s="1">
         <v>122</v>
       </c>
@@ -22267,7 +22272,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="612" customHeight="1" spans="1:10">
+    <row r="612" hidden="1" customHeight="1" spans="1:10">
       <c r="A612" s="4">
         <v>661</v>
       </c>
@@ -22290,7 +22295,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="613" customHeight="1" spans="1:10">
+    <row r="613" hidden="1" customHeight="1" spans="1:10">
       <c r="A613" s="1">
         <v>112</v>
       </c>
@@ -22313,7 +22318,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="614" customHeight="1" spans="1:10">
+    <row r="614" hidden="1" customHeight="1" spans="1:10">
       <c r="A614" s="4">
         <v>728</v>
       </c>
@@ -22336,7 +22341,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="615" customHeight="1" spans="1:10">
+    <row r="615" hidden="1" customHeight="1" spans="1:10">
       <c r="A615" s="4">
         <v>487</v>
       </c>
@@ -22359,7 +22364,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="616" customHeight="1" spans="1:10">
+    <row r="616" hidden="1" customHeight="1" spans="1:10">
       <c r="A616" s="4">
         <v>684</v>
       </c>
@@ -22382,7 +22387,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="617" customHeight="1" spans="1:10">
+    <row r="617" hidden="1" customHeight="1" spans="1:10">
       <c r="A617" s="1">
         <v>85</v>
       </c>
@@ -22405,7 +22410,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="618" customHeight="1" spans="1:10">
+    <row r="618" hidden="1" customHeight="1" spans="1:10">
       <c r="A618" s="1">
         <v>319</v>
       </c>
@@ -22428,7 +22433,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="619" customHeight="1" spans="1:10">
+    <row r="619" hidden="1" customHeight="1" spans="1:10">
       <c r="A619" s="4">
         <v>493</v>
       </c>
@@ -22451,7 +22456,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="620" customHeight="1" spans="1:10">
+    <row r="620" hidden="1" customHeight="1" spans="1:10">
       <c r="A620" s="4">
         <v>675</v>
       </c>
@@ -22474,7 +22479,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="621" customHeight="1" spans="1:10">
+    <row r="621" hidden="1" customHeight="1" spans="1:10">
       <c r="A621" s="4">
         <v>737</v>
       </c>
@@ -22497,7 +22502,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="622" customHeight="1" spans="1:10">
+    <row r="622" hidden="1" customHeight="1" spans="1:10">
       <c r="A622" s="1">
         <v>142</v>
       </c>
@@ -22520,7 +22525,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="623" customHeight="1" spans="1:10">
+    <row r="623" hidden="1" customHeight="1" spans="1:10">
       <c r="A623" s="1">
         <v>20</v>
       </c>
@@ -22546,7 +22551,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="624" customHeight="1" spans="1:10">
+    <row r="624" hidden="1" customHeight="1" spans="1:10">
       <c r="A624" s="4">
         <v>659</v>
       </c>
@@ -22569,7 +22574,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="625" customHeight="1" spans="1:10">
+    <row r="625" hidden="1" customHeight="1" spans="1:10">
       <c r="A625" s="4">
         <v>384</v>
       </c>
@@ -22592,7 +22597,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="626" customHeight="1" spans="1:10">
+    <row r="626" hidden="1" customHeight="1" spans="1:10">
       <c r="A626" s="4">
         <v>381</v>
       </c>
@@ -22615,7 +22620,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="627" customHeight="1" spans="1:10">
+    <row r="627" hidden="1" customHeight="1" spans="1:10">
       <c r="A627" s="1">
         <v>58</v>
       </c>
@@ -22638,7 +22643,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="628" customHeight="1" spans="1:10">
+    <row r="628" hidden="1" customHeight="1" spans="1:10">
       <c r="A628" s="4">
         <v>589</v>
       </c>
@@ -22661,7 +22666,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="629" customHeight="1" spans="1:10">
+    <row r="629" hidden="1" customHeight="1" spans="1:10">
       <c r="A629" s="4">
         <v>726</v>
       </c>
@@ -22684,7 +22689,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="630" customHeight="1" spans="1:10">
+    <row r="630" hidden="1" customHeight="1" spans="1:10">
       <c r="A630" s="4">
         <v>470</v>
       </c>
@@ -22707,7 +22712,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="631" customHeight="1" spans="1:10">
+    <row r="631" hidden="1" customHeight="1" spans="1:10">
       <c r="A631" s="1">
         <v>116</v>
       </c>
@@ -22730,7 +22735,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="632" customHeight="1" spans="1:10">
+    <row r="632" hidden="1" customHeight="1" spans="1:10">
       <c r="A632" s="4">
         <v>672</v>
       </c>
@@ -22753,7 +22758,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="633" customHeight="1" spans="1:10">
+    <row r="633" hidden="1" customHeight="1" spans="1:10">
       <c r="A633" s="4">
         <v>525</v>
       </c>
@@ -22776,7 +22781,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="634" customHeight="1" spans="1:10">
+    <row r="634" hidden="1" customHeight="1" spans="1:10">
       <c r="A634" s="4">
         <v>526</v>
       </c>
@@ -22799,7 +22804,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="635" customHeight="1" spans="1:10">
+    <row r="635" hidden="1" customHeight="1" spans="1:10">
       <c r="A635" s="1">
         <v>296</v>
       </c>
@@ -22822,7 +22827,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="636" customHeight="1" spans="1:10">
+    <row r="636" hidden="1" customHeight="1" spans="1:10">
       <c r="A636" s="1">
         <v>244</v>
       </c>
@@ -22845,7 +22850,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="637" customHeight="1" spans="1:10">
+    <row r="637" hidden="1" customHeight="1" spans="1:10">
       <c r="A637" s="1">
         <v>245</v>
       </c>
@@ -22868,7 +22873,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="638" customHeight="1" spans="1:10">
+    <row r="638" hidden="1" customHeight="1" spans="1:10">
       <c r="A638" s="1">
         <v>106</v>
       </c>
@@ -22891,7 +22896,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="639" customHeight="1" spans="1:10">
+    <row r="639" hidden="1" customHeight="1" spans="1:10">
       <c r="A639" s="4">
         <v>732</v>
       </c>
@@ -22914,7 +22919,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="640" customHeight="1" spans="1:10">
+    <row r="640" hidden="1" customHeight="1" spans="1:10">
       <c r="A640" s="4">
         <v>558</v>
       </c>
@@ -22937,7 +22942,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="641" customHeight="1" spans="1:10">
+    <row r="641" hidden="1" customHeight="1" spans="1:10">
       <c r="A641" s="4">
         <v>671</v>
       </c>
@@ -22960,7 +22965,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="642" customHeight="1" spans="1:10">
+    <row r="642" hidden="1" customHeight="1" spans="1:10">
       <c r="A642" s="1">
         <v>262</v>
       </c>
@@ -22983,7 +22988,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="643" customHeight="1" spans="1:10">
+    <row r="643" hidden="1" customHeight="1" spans="1:10">
       <c r="A643" s="4">
         <v>677</v>
       </c>
@@ -23006,7 +23011,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="644" customHeight="1" spans="1:10">
+    <row r="644" hidden="1" customHeight="1" spans="1:10">
       <c r="A644" s="1">
         <v>166</v>
       </c>
@@ -23029,7 +23034,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="645" customHeight="1" spans="1:10">
+    <row r="645" hidden="1" customHeight="1" spans="1:10">
       <c r="A645" s="4">
         <v>598</v>
       </c>
@@ -23052,7 +23057,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="646" customHeight="1" spans="1:10">
+    <row r="646" hidden="1" customHeight="1" spans="1:10">
       <c r="A646" s="4">
         <v>667</v>
       </c>
@@ -23075,7 +23080,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="647" customHeight="1" spans="1:10">
+    <row r="647" hidden="1" customHeight="1" spans="1:10">
       <c r="A647" s="1">
         <v>303</v>
       </c>
@@ -23098,7 +23103,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="648" customHeight="1" spans="1:10">
+    <row r="648" hidden="1" customHeight="1" spans="1:10">
       <c r="A648" s="1">
         <v>282</v>
       </c>
@@ -23121,7 +23126,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="649" customHeight="1" spans="1:10">
+    <row r="649" hidden="1" customHeight="1" spans="1:10">
       <c r="A649" s="4">
         <v>512</v>
       </c>
@@ -23144,7 +23149,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="650" customHeight="1" spans="1:10">
+    <row r="650" hidden="1" customHeight="1" spans="1:10">
       <c r="A650" s="1">
         <v>229</v>
       </c>
@@ -23167,7 +23172,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="651" customHeight="1" spans="1:10">
+    <row r="651" hidden="1" customHeight="1" spans="1:10">
       <c r="A651" s="4">
         <v>673</v>
       </c>
@@ -23190,7 +23195,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="652" customHeight="1" spans="1:10">
+    <row r="652" hidden="1" customHeight="1" spans="1:10">
       <c r="A652" s="4">
         <v>390</v>
       </c>
@@ -23213,7 +23218,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="653" customHeight="1" spans="1:10">
+    <row r="653" hidden="1" customHeight="1" spans="1:10">
       <c r="A653" s="4">
         <v>740</v>
       </c>
@@ -23236,7 +23241,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="654" customHeight="1" spans="1:10">
+    <row r="654" hidden="1" customHeight="1" spans="1:10">
       <c r="A654" s="4">
         <v>674</v>
       </c>
@@ -23259,7 +23264,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="655" customHeight="1" spans="1:10">
+    <row r="655" hidden="1" customHeight="1" spans="1:10">
       <c r="A655" s="4">
         <v>432</v>
       </c>
@@ -23282,7 +23287,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="656" customHeight="1" spans="1:10">
+    <row r="656" hidden="1" customHeight="1" spans="1:10">
       <c r="A656" s="4">
         <v>552</v>
       </c>
@@ -23305,7 +23310,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="657" customHeight="1" spans="1:10">
+    <row r="657" hidden="1" customHeight="1" spans="1:10">
       <c r="A657" s="4">
         <v>652</v>
       </c>
@@ -23328,7 +23333,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="658" customHeight="1" spans="1:10">
+    <row r="658" hidden="1" customHeight="1" spans="1:10">
       <c r="A658" s="4">
         <v>670</v>
       </c>
@@ -23351,7 +23356,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="659" customHeight="1" spans="1:10">
+    <row r="659" hidden="1" customHeight="1" spans="1:10">
       <c r="A659" s="1">
         <v>283</v>
       </c>
@@ -23374,7 +23379,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="660" customHeight="1" spans="1:10">
+    <row r="660" hidden="1" customHeight="1" spans="1:10">
       <c r="A660" s="1">
         <v>202</v>
       </c>
@@ -23397,7 +23402,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="661" customHeight="1" spans="1:10">
+    <row r="661" hidden="1" customHeight="1" spans="1:10">
       <c r="A661" s="4">
         <v>657</v>
       </c>
@@ -23420,7 +23425,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="662" customHeight="1" spans="1:10">
+    <row r="662" hidden="1" customHeight="1" spans="1:10">
       <c r="A662" s="1">
         <v>281</v>
       </c>
@@ -23443,7 +23448,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="663" customHeight="1" spans="1:10">
+    <row r="663" hidden="1" customHeight="1" spans="1:10">
       <c r="A663" s="1">
         <v>332</v>
       </c>
@@ -23466,7 +23471,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="664" customHeight="1" spans="1:10">
+    <row r="664" hidden="1" customHeight="1" spans="1:10">
       <c r="A664" s="4">
         <v>394</v>
       </c>
@@ -23489,7 +23494,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="665" customHeight="1" spans="1:10">
+    <row r="665" hidden="1" customHeight="1" spans="1:10">
       <c r="A665" s="4">
         <v>517</v>
       </c>
@@ -23512,7 +23517,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="666" customHeight="1" spans="1:10">
+    <row r="666" hidden="1" customHeight="1" spans="1:10">
       <c r="A666" s="4">
         <v>516</v>
       </c>
@@ -23535,7 +23540,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="667" customHeight="1" spans="1:10">
+    <row r="667" hidden="1" customHeight="1" spans="1:10">
       <c r="A667" s="4">
         <v>519</v>
       </c>
@@ -23558,7 +23563,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="668" customHeight="1" spans="1:10">
+    <row r="668" hidden="1" customHeight="1" spans="1:10">
       <c r="A668" s="1">
         <v>279</v>
       </c>
@@ -23581,7 +23586,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="669" customHeight="1" spans="1:10">
+    <row r="669" hidden="1" customHeight="1" spans="1:10">
       <c r="A669" s="4">
         <v>668</v>
       </c>
@@ -23604,7 +23609,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="670" customHeight="1" spans="1:10">
+    <row r="670" hidden="1" customHeight="1" spans="1:10">
       <c r="A670" s="1">
         <v>285</v>
       </c>
@@ -23627,7 +23632,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="671" customHeight="1" spans="1:10">
+    <row r="671" hidden="1" customHeight="1" spans="1:10">
       <c r="A671" s="4">
         <v>463</v>
       </c>
@@ -23650,7 +23655,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="672" customHeight="1" spans="1:10">
+    <row r="672" hidden="1" customHeight="1" spans="1:10">
       <c r="A672" s="4">
         <v>735</v>
       </c>
@@ -23673,7 +23678,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="673" customHeight="1" spans="1:10">
+    <row r="673" hidden="1" customHeight="1" spans="1:10">
       <c r="A673" s="1">
         <v>177</v>
       </c>
@@ -23696,7 +23701,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="674" customHeight="1" spans="1:10">
+    <row r="674" hidden="1" customHeight="1" spans="1:10">
       <c r="A674" s="1">
         <v>84</v>
       </c>
@@ -23719,7 +23724,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="675" customHeight="1" spans="1:10">
+    <row r="675" hidden="1" customHeight="1" spans="1:10">
       <c r="A675" s="4">
         <v>484</v>
       </c>
@@ -23742,7 +23747,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="676" customHeight="1" spans="1:10">
+    <row r="676" hidden="1" customHeight="1" spans="1:10">
       <c r="A676" s="1">
         <v>21</v>
       </c>
@@ -23768,7 +23773,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="677" customHeight="1" spans="1:10">
+    <row r="677" hidden="1" customHeight="1" spans="1:10">
       <c r="A677" s="1">
         <v>241</v>
       </c>
@@ -23791,7 +23796,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="678" customHeight="1" spans="1:10">
+    <row r="678" hidden="1" customHeight="1" spans="1:10">
       <c r="A678" s="4">
         <v>601</v>
       </c>
@@ -23814,7 +23819,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="679" customHeight="1" spans="1:10">
+    <row r="679" hidden="1" customHeight="1" spans="1:10">
       <c r="A679" s="1">
         <v>200</v>
       </c>
@@ -23837,7 +23842,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="680" customHeight="1" spans="1:10">
+    <row r="680" hidden="1" customHeight="1" spans="1:10">
       <c r="A680" s="4">
         <v>669</v>
       </c>
@@ -23860,7 +23865,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="681" customHeight="1" spans="1:10">
+    <row r="681" hidden="1" customHeight="1" spans="1:10">
       <c r="A681" s="1">
         <v>40</v>
       </c>
@@ -23883,7 +23888,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="682" customHeight="1" spans="1:10">
+    <row r="682" hidden="1" customHeight="1" spans="1:10">
       <c r="A682" s="4">
         <v>464</v>
       </c>
@@ -23906,7 +23911,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="683" customHeight="1" spans="1:10">
+    <row r="683" hidden="1" customHeight="1" spans="1:10">
       <c r="A683" s="4">
         <v>431</v>
       </c>
@@ -23929,7 +23934,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="684" customHeight="1" spans="1:10">
+    <row r="684" hidden="1" customHeight="1" spans="1:10">
       <c r="A684" s="4">
         <v>488</v>
       </c>
@@ -23952,7 +23957,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="685" customHeight="1" spans="1:10">
+    <row r="685" hidden="1" customHeight="1" spans="1:10">
       <c r="A685" s="1">
         <v>284</v>
       </c>
@@ -23975,7 +23980,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="686" hidden="1" customHeight="1" spans="1:10">
+    <row r="686" customHeight="1" spans="1:10">
       <c r="A686" s="1">
         <v>4</v>
       </c>
@@ -23999,7 +24004,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="687" hidden="1" customHeight="1" spans="1:10">
+    <row r="687" customHeight="1" spans="1:10">
       <c r="A687" s="4">
         <v>714</v>
       </c>
@@ -24020,7 +24025,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="688" hidden="1" customHeight="1" spans="1:10">
+    <row r="688" customHeight="1" spans="1:10">
       <c r="A688" s="4">
         <v>455</v>
       </c>
@@ -24041,7 +24046,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="689" hidden="1" customHeight="1" spans="1:10">
+    <row r="689" customHeight="1" spans="1:10">
       <c r="A689" s="4">
         <v>546</v>
       </c>
@@ -24062,7 +24067,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="690" hidden="1" customHeight="1" spans="1:10">
+    <row r="690" customHeight="1" spans="1:10">
       <c r="A690" s="4">
         <v>545</v>
       </c>
@@ -24083,7 +24088,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="691" hidden="1" customHeight="1" spans="1:10">
+    <row r="691" customHeight="1" spans="1:10">
       <c r="A691" s="4">
         <v>550</v>
       </c>
@@ -24104,7 +24109,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="692" hidden="1" customHeight="1" spans="1:10">
+    <row r="692" customHeight="1" spans="1:10">
       <c r="A692" s="1">
         <v>318</v>
       </c>
@@ -24125,7 +24130,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="693" hidden="1" customHeight="1" spans="1:10">
+    <row r="693" customHeight="1" spans="1:10">
       <c r="A693" s="4">
         <v>551</v>
       </c>
@@ -24146,7 +24151,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="694" hidden="1" customHeight="1" spans="1:10">
+    <row r="694" customHeight="1" spans="1:10">
       <c r="A694" s="1">
         <v>271</v>
       </c>
@@ -24167,7 +24172,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="695" hidden="1" customHeight="1" spans="1:10">
+    <row r="695" customHeight="1" spans="1:10">
       <c r="A695" s="4">
         <v>492</v>
       </c>
@@ -24188,7 +24193,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="696" hidden="1" customHeight="1" spans="1:10">
+    <row r="696" customHeight="1" spans="1:10">
       <c r="A696" s="4">
         <v>639</v>
       </c>
@@ -24209,7 +24214,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="697" hidden="1" customHeight="1" spans="1:10">
+    <row r="697" customHeight="1" spans="1:10">
       <c r="A697" s="4">
         <v>634</v>
       </c>
@@ -24230,7 +24235,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="698" hidden="1" customHeight="1" spans="1:10">
+    <row r="698" customHeight="1" spans="1:10">
       <c r="A698" s="4">
         <v>561</v>
       </c>
@@ -24251,7 +24256,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="699" hidden="1" customHeight="1" spans="1:10">
+    <row r="699" customHeight="1" spans="1:10">
       <c r="A699" s="4">
         <v>556</v>
       </c>
@@ -24272,7 +24277,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="700" hidden="1" customHeight="1" spans="1:10">
+    <row r="700" customHeight="1" spans="1:10">
       <c r="A700" s="4">
         <v>685</v>
       </c>
@@ -24293,7 +24298,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="701" hidden="1" customHeight="1" spans="1:10">
+    <row r="701" customHeight="1" spans="1:10">
       <c r="A701" s="4">
         <v>586</v>
       </c>
@@ -24314,7 +24319,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="702" hidden="1" customHeight="1" spans="1:10">
+    <row r="702" customHeight="1" spans="1:10">
       <c r="A702" s="4">
         <v>413</v>
       </c>
@@ -24335,7 +24340,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="703" hidden="1" customHeight="1" spans="1:10">
+    <row r="703" customHeight="1" spans="1:10">
       <c r="A703" s="4">
         <v>729</v>
       </c>
@@ -24356,7 +24361,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="704" hidden="1" customHeight="1" spans="1:10">
+    <row r="704" customHeight="1" spans="1:10">
       <c r="A704" s="4">
         <v>362</v>
       </c>
@@ -24377,7 +24382,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="705" hidden="1" customHeight="1" spans="1:10">
+    <row r="705" customHeight="1" spans="1:10">
       <c r="A705" s="4">
         <v>549</v>
       </c>
@@ -24398,7 +24403,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="706" hidden="1" customHeight="1" spans="1:10">
+    <row r="706" customHeight="1" spans="1:10">
       <c r="A706" s="4">
         <v>418</v>
       </c>
@@ -24419,7 +24424,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="707" hidden="1" customHeight="1" spans="1:10">
+    <row r="707" customHeight="1" spans="1:10">
       <c r="A707" s="4">
         <v>548</v>
       </c>
@@ -24440,7 +24445,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="708" hidden="1" customHeight="1" spans="1:10">
+    <row r="708" customHeight="1" spans="1:10">
       <c r="A708" s="4">
         <v>544</v>
       </c>
@@ -24461,7 +24466,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="709" hidden="1" customHeight="1" spans="1:10">
+    <row r="709" customHeight="1" spans="1:10">
       <c r="A709" s="1">
         <v>342</v>
       </c>
@@ -24482,7 +24487,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="710" hidden="1" customHeight="1" spans="1:10">
+    <row r="710" customHeight="1" spans="1:10">
       <c r="A710" s="4">
         <v>530</v>
       </c>
@@ -24503,7 +24508,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="711" hidden="1" customHeight="1" spans="1:10">
+    <row r="711" customHeight="1" spans="1:10">
       <c r="A711" s="4">
         <v>392</v>
       </c>
@@ -24524,7 +24529,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="712" hidden="1" customHeight="1" spans="1:10">
+    <row r="712" customHeight="1" spans="1:10">
       <c r="A712" s="4">
         <v>505</v>
       </c>
@@ -24545,7 +24550,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="713" hidden="1" customHeight="1" spans="1:10">
+    <row r="713" customHeight="1" spans="1:10">
       <c r="A713" s="1">
         <v>353</v>
       </c>
@@ -24566,7 +24571,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="714" hidden="1" customHeight="1" spans="1:10">
+    <row r="714" customHeight="1" spans="1:10">
       <c r="A714" s="1">
         <v>155</v>
       </c>
@@ -24587,7 +24592,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="715" hidden="1" customHeight="1" spans="1:10">
+    <row r="715" customHeight="1" spans="1:10">
       <c r="A715" s="1">
         <v>292</v>
       </c>
@@ -24608,7 +24613,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="716" hidden="1" customHeight="1" spans="1:10">
+    <row r="716" customHeight="1" spans="1:10">
       <c r="A716" s="4">
         <v>444</v>
       </c>
@@ -24629,7 +24634,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="717" hidden="1" customHeight="1" spans="1:10">
+    <row r="717" customHeight="1" spans="1:10">
       <c r="A717" s="4">
         <v>531</v>
       </c>
@@ -24650,7 +24655,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="718" hidden="1" customHeight="1" spans="1:10">
+    <row r="718" customHeight="1" spans="1:10">
       <c r="A718" s="4">
         <v>642</v>
       </c>
@@ -24671,7 +24676,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="719" hidden="1" customHeight="1" spans="1:10">
+    <row r="719" customHeight="1" spans="1:10">
       <c r="A719" s="1">
         <v>36</v>
       </c>
@@ -24690,7 +24695,7 @@
       </c>
       <c r="J719" s="5"/>
     </row>
-    <row r="720" hidden="1" customHeight="1" spans="1:10">
+    <row r="720" customHeight="1" spans="1:10">
       <c r="A720" s="1">
         <v>103</v>
       </c>
@@ -24709,7 +24714,7 @@
       </c>
       <c r="J720" s="5"/>
     </row>
-    <row r="721" hidden="1" customHeight="1" spans="1:10">
+    <row r="721" customHeight="1" spans="1:10">
       <c r="A721" s="1">
         <v>128</v>
       </c>
@@ -24728,7 +24733,7 @@
       </c>
       <c r="J721" s="5"/>
     </row>
-    <row r="722" hidden="1" customHeight="1" spans="1:10">
+    <row r="722" customHeight="1" spans="1:10">
       <c r="A722" s="1">
         <v>158</v>
       </c>
@@ -24747,7 +24752,7 @@
       </c>
       <c r="J722" s="5"/>
     </row>
-    <row r="723" hidden="1" customHeight="1" spans="1:10">
+    <row r="723" customHeight="1" spans="1:10">
       <c r="A723" s="1">
         <v>162</v>
       </c>
@@ -24766,7 +24771,7 @@
       </c>
       <c r="J723" s="5"/>
     </row>
-    <row r="724" hidden="1" customHeight="1" spans="1:10">
+    <row r="724" customHeight="1" spans="1:10">
       <c r="A724" s="1">
         <v>214</v>
       </c>
@@ -24785,7 +24790,7 @@
       </c>
       <c r="J724" s="5"/>
     </row>
-    <row r="725" hidden="1" customHeight="1" spans="1:10">
+    <row r="725" customHeight="1" spans="1:10">
       <c r="A725" s="1">
         <v>315</v>
       </c>
@@ -24804,7 +24809,7 @@
       </c>
       <c r="J725" s="5"/>
     </row>
-    <row r="726" hidden="1" customHeight="1" spans="1:10">
+    <row r="726" customHeight="1" spans="1:10">
       <c r="A726" s="1">
         <v>328</v>
       </c>
@@ -24823,7 +24828,7 @@
       </c>
       <c r="J726" s="5"/>
     </row>
-    <row r="727" hidden="1" customHeight="1" spans="1:10">
+    <row r="727" customHeight="1" spans="1:10">
       <c r="A727" s="1">
         <v>341</v>
       </c>
@@ -24842,7 +24847,7 @@
       </c>
       <c r="J727" s="5"/>
     </row>
-    <row r="728" hidden="1" customHeight="1" spans="1:10">
+    <row r="728" customHeight="1" spans="1:10">
       <c r="A728" s="4">
         <v>371</v>
       </c>
@@ -24861,7 +24866,7 @@
       </c>
       <c r="J728" s="5"/>
     </row>
-    <row r="729" hidden="1" customHeight="1" spans="1:10">
+    <row r="729" customHeight="1" spans="1:10">
       <c r="A729" s="4">
         <v>377</v>
       </c>
@@ -24880,7 +24885,7 @@
       </c>
       <c r="J729" s="5"/>
     </row>
-    <row r="730" hidden="1" customHeight="1" spans="1:10">
+    <row r="730" customHeight="1" spans="1:10">
       <c r="A730" s="4">
         <v>379</v>
       </c>
@@ -24899,7 +24904,7 @@
       </c>
       <c r="J730" s="5"/>
     </row>
-    <row r="731" hidden="1" customHeight="1" spans="1:10">
+    <row r="731" customHeight="1" spans="1:10">
       <c r="A731" s="4">
         <v>398</v>
       </c>
@@ -24918,7 +24923,7 @@
       </c>
       <c r="J731" s="5"/>
     </row>
-    <row r="732" hidden="1" customHeight="1" spans="1:10">
+    <row r="732" customHeight="1" spans="1:10">
       <c r="A732" s="4">
         <v>506</v>
       </c>
@@ -24937,7 +24942,7 @@
       </c>
       <c r="J732" s="5"/>
     </row>
-    <row r="733" hidden="1" customHeight="1" spans="1:10">
+    <row r="733" customHeight="1" spans="1:10">
       <c r="A733" s="4">
         <v>515</v>
       </c>
@@ -24956,7 +24961,7 @@
       </c>
       <c r="J733" s="5"/>
     </row>
-    <row r="734" hidden="1" customHeight="1" spans="1:10">
+    <row r="734" customHeight="1" spans="1:10">
       <c r="A734" s="4">
         <v>594</v>
       </c>
@@ -24975,7 +24980,7 @@
       </c>
       <c r="J734" s="5"/>
     </row>
-    <row r="735" hidden="1" customHeight="1" spans="1:10">
+    <row r="735" customHeight="1" spans="1:10">
       <c r="A735" s="4">
         <v>603</v>
       </c>
@@ -24994,7 +24999,7 @@
       </c>
       <c r="J735" s="5"/>
     </row>
-    <row r="736" hidden="1" customHeight="1" spans="1:10">
+    <row r="736" customHeight="1" spans="1:10">
       <c r="A736" s="4">
         <v>604</v>
       </c>
@@ -25013,7 +25018,7 @@
       </c>
       <c r="J736" s="5"/>
     </row>
-    <row r="737" hidden="1" customHeight="1" spans="1:10">
+    <row r="737" customHeight="1" spans="1:10">
       <c r="A737" s="4">
         <v>638</v>
       </c>
@@ -25032,7 +25037,7 @@
       </c>
       <c r="J737" s="5"/>
     </row>
-    <row r="738" hidden="1" customHeight="1" spans="1:10">
+    <row r="738" customHeight="1" spans="1:10">
       <c r="A738" s="4">
         <v>640</v>
       </c>
@@ -25051,7 +25056,7 @@
       </c>
       <c r="J738" s="5"/>
     </row>
-    <row r="739" hidden="1" customHeight="1" spans="1:10">
+    <row r="739" customHeight="1" spans="1:10">
       <c r="A739" s="4">
         <v>649</v>
       </c>
@@ -25070,7 +25075,7 @@
       </c>
       <c r="J739" s="5"/>
     </row>
-    <row r="740" hidden="1" customHeight="1" spans="1:10">
+    <row r="740" customHeight="1" spans="1:10">
       <c r="A740" s="4">
         <v>665</v>
       </c>
@@ -25089,7 +25094,7 @@
       </c>
       <c r="J740" s="5"/>
     </row>
-    <row r="741" hidden="1" customHeight="1" spans="1:10">
+    <row r="741" customHeight="1" spans="1:10">
       <c r="A741" s="4">
         <v>708</v>
       </c>
@@ -25108,7 +25113,7 @@
       </c>
       <c r="J741" s="5"/>
     </row>
-    <row r="742" hidden="1" customHeight="1" spans="1:10">
+    <row r="742" customHeight="1" spans="1:10">
       <c r="A742" s="4">
         <v>709</v>
       </c>
@@ -25597,7 +25602,7 @@
     <hyperlink ref="J433" r:id="rId454" display="http://www.ncbi.nlm.nih.gov/pubmed/18438109"/>
     <hyperlink ref="J110" r:id="rId455" display="https://www.ncbi.nlm.nih.gov/pubmed/26363985"/>
     <hyperlink ref="J101" r:id="rId456" display="https://www.ncbi.nlm.nih.gov/pubmed/27001590"/>
-    <hyperlink ref="J192" r:id="rId457" display="https://doi.org/10.1200/JCO.2016.34.15_suppl.1006"/>
+    <hyperlink ref="J192" r:id="rId457" display="https://doi.org/10.1200/JCO.2016.34.15_suppl.1006" tooltip="https://doi.org/10.1200/JCO.2016.34.15_suppl.1006"/>
     <hyperlink ref="J70" r:id="rId458" display="https://www.ncbi.nlm.nih.gov/pubmed/29777404"/>
     <hyperlink ref="J426" r:id="rId459" display="http://www.ncbi.nlm.nih.gov/pubmed/18561551"/>
     <hyperlink ref="J521" r:id="rId460" display="http://www.ncbi.nlm.nih.gov/pubmed/16702591"/>
